--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -47,7 +47,7 @@
     <t>AttrValueList</t>
   </si>
   <si>
-    <t>Quality</t>
+    <t>Count</t>
   </si>
   <si>
     <t>Des</t>
@@ -62,112 +62,112 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>战士1级套装</t>
-  </si>
-  <si>
-    <t>法师1级套装</t>
-  </si>
-  <si>
-    <t>道士1级套装</t>
-  </si>
-  <si>
-    <t>战士10级套装</t>
-  </si>
-  <si>
-    <t>法师10级套装</t>
-  </si>
-  <si>
-    <t>道士10级套装</t>
-  </si>
-  <si>
-    <t>战士20级套装</t>
-  </si>
-  <si>
-    <t>法师20级套装</t>
-  </si>
-  <si>
-    <t>道士20级套装</t>
-  </si>
-  <si>
-    <t>战士30级套装</t>
-  </si>
-  <si>
-    <t>法师30级套装</t>
-  </si>
-  <si>
-    <t>道士30级套装</t>
-  </si>
-  <si>
-    <t>战士40级套装</t>
-  </si>
-  <si>
-    <t>法师40级套装</t>
-  </si>
-  <si>
-    <t>道士40级套装</t>
-  </si>
-  <si>
-    <t>战士50级套装</t>
-  </si>
-  <si>
-    <t>法师50级套装</t>
-  </si>
-  <si>
-    <t>道士50级套装</t>
-  </si>
-  <si>
-    <t>战士60级套装</t>
-  </si>
-  <si>
-    <t>法师60级套装</t>
-  </si>
-  <si>
-    <t>道士60级套装</t>
-  </si>
-  <si>
-    <t>战士70级套装</t>
-  </si>
-  <si>
-    <t>法师70级套装</t>
-  </si>
-  <si>
-    <t>道士70级套装</t>
-  </si>
-  <si>
-    <t>战士80级套装</t>
-  </si>
-  <si>
-    <t>法师80级套装</t>
-  </si>
-  <si>
-    <t>道士80级套装</t>
-  </si>
-  <si>
-    <t>战士90级套装</t>
-  </si>
-  <si>
-    <t>法师90级套装</t>
-  </si>
-  <si>
-    <t>道士90级套装</t>
-  </si>
-  <si>
-    <t>战士100级套装</t>
-  </si>
-  <si>
-    <t>法师100级套装</t>
-  </si>
-  <si>
-    <t>道士100级套装</t>
-  </si>
-  <si>
-    <t>战士110级套装</t>
-  </si>
-  <si>
-    <t>法师110级套装</t>
-  </si>
-  <si>
-    <t>道士110级套装</t>
+    <t>0级战装</t>
+  </si>
+  <si>
+    <t>0级法装</t>
+  </si>
+  <si>
+    <t>0级道装</t>
+  </si>
+  <si>
+    <t>10级战装</t>
+  </si>
+  <si>
+    <t>10级法装</t>
+  </si>
+  <si>
+    <t>10级道装</t>
+  </si>
+  <si>
+    <t>20级战装</t>
+  </si>
+  <si>
+    <t>20级法装</t>
+  </si>
+  <si>
+    <t>20级道装</t>
+  </si>
+  <si>
+    <t>30级战装</t>
+  </si>
+  <si>
+    <t>30级法装</t>
+  </si>
+  <si>
+    <t>30级道装</t>
+  </si>
+  <si>
+    <t>40级战装</t>
+  </si>
+  <si>
+    <t>40级法装</t>
+  </si>
+  <si>
+    <t>40级道装</t>
+  </si>
+  <si>
+    <t>50级战装</t>
+  </si>
+  <si>
+    <t>50级法装</t>
+  </si>
+  <si>
+    <t>50级道装</t>
+  </si>
+  <si>
+    <t>60级战装</t>
+  </si>
+  <si>
+    <t>60级法装</t>
+  </si>
+  <si>
+    <t>60级道装</t>
+  </si>
+  <si>
+    <t>70级战装</t>
+  </si>
+  <si>
+    <t>70级法装</t>
+  </si>
+  <si>
+    <t>70级道装</t>
+  </si>
+  <si>
+    <t>80级战装</t>
+  </si>
+  <si>
+    <t>80级法装</t>
+  </si>
+  <si>
+    <t>80级道装</t>
+  </si>
+  <si>
+    <t>90级战装</t>
+  </si>
+  <si>
+    <t>90级法装</t>
+  </si>
+  <si>
+    <t>90级道装</t>
+  </si>
+  <si>
+    <t>100级战装</t>
+  </si>
+  <si>
+    <t>100级法装</t>
+  </si>
+  <si>
+    <t>100级道装</t>
+  </si>
+  <si>
+    <t>110级战装</t>
+  </si>
+  <si>
+    <t>110级法装</t>
+  </si>
+  <si>
+    <t>110级道装</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1135,8 @@
     <col min="6" max="6" width="12.9166666666667" style="1" customWidth="1"/>
     <col min="7" max="8" width="12.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="26.75" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="14.9166666666667" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="3:9">
@@ -1221,7 +1222,9 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1232,14 +1235,16 @@
         <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1250,14 +1255,16 @@
         <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1268,13 +1275,16 @@
         <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:9">
       <c r="C9" s="1">
         <v>4</v>
       </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1285,13 +1295,16 @@
         <v>2</v>
       </c>
       <c r="H9" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:9">
       <c r="C10" s="1">
         <v>5</v>
       </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1302,13 +1315,16 @@
         <v>2</v>
       </c>
       <c r="H10" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:9">
       <c r="C11" s="1">
         <v>6</v>
       </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1" t="s">
         <v>16</v>
       </c>
@@ -1319,13 +1335,16 @@
         <v>2</v>
       </c>
       <c r="H11" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:9">
       <c r="C12" s="1">
         <v>7</v>
       </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>17</v>
       </c>
@@ -1336,13 +1355,16 @@
         <v>3</v>
       </c>
       <c r="H12" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:9">
       <c r="C13" s="1">
         <v>8</v>
       </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
@@ -1353,13 +1375,16 @@
         <v>3</v>
       </c>
       <c r="H13" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:9">
       <c r="C14" s="1">
         <v>9</v>
       </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1370,13 +1395,16 @@
         <v>3</v>
       </c>
       <c r="H14" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:9">
       <c r="C15" s="1">
         <v>10</v>
       </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,13 +1415,16 @@
         <v>4</v>
       </c>
       <c r="H15" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:9">
       <c r="C16" s="1">
         <v>11</v>
       </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1" t="s">
         <v>21</v>
       </c>
@@ -1404,13 +1435,16 @@
         <v>4</v>
       </c>
       <c r="H16" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
       <c r="C17" s="1">
         <v>12</v>
       </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
@@ -1421,13 +1455,16 @@
         <v>4</v>
       </c>
       <c r="H17" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:8">
       <c r="C18" s="1">
         <v>13</v>
       </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
       <c r="E18" s="1" t="s">
         <v>23</v>
       </c>
@@ -1438,13 +1475,16 @@
         <v>5</v>
       </c>
       <c r="H18" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:8">
       <c r="C19" s="1">
         <v>14</v>
       </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
       <c r="E19" s="1" t="s">
         <v>24</v>
       </c>
@@ -1455,13 +1495,16 @@
         <v>5</v>
       </c>
       <c r="H19" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:8">
       <c r="C20" s="1">
         <v>15</v>
       </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
       <c r="E20" s="1" t="s">
         <v>25</v>
       </c>
@@ -1472,13 +1515,16 @@
         <v>5</v>
       </c>
       <c r="H20" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:8">
       <c r="C21" s="1">
         <v>16</v>
       </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
       <c r="E21" s="1" t="s">
         <v>26</v>
       </c>
@@ -1489,13 +1535,16 @@
         <v>6</v>
       </c>
       <c r="H21" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:8">
       <c r="C22" s="1">
         <v>17</v>
       </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
       <c r="E22" s="1" t="s">
         <v>27</v>
       </c>
@@ -1506,13 +1555,16 @@
         <v>6</v>
       </c>
       <c r="H22" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="1">
         <v>18</v>
       </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
       <c r="E23" s="1" t="s">
         <v>28</v>
       </c>
@@ -1523,13 +1575,16 @@
         <v>6</v>
       </c>
       <c r="H23" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="1">
         <v>19</v>
       </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
       <c r="E24" s="1" t="s">
         <v>29</v>
       </c>
@@ -1540,13 +1595,16 @@
         <v>7</v>
       </c>
       <c r="H24" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
       <c r="C25" s="1">
         <v>20</v>
       </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
       <c r="E25" s="1" t="s">
         <v>30</v>
       </c>
@@ -1557,13 +1615,16 @@
         <v>7</v>
       </c>
       <c r="H25" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
       <c r="C26" s="1">
         <v>21</v>
       </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
       <c r="E26" s="1" t="s">
         <v>31</v>
       </c>
@@ -1574,13 +1635,16 @@
         <v>7</v>
       </c>
       <c r="H26" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
       <c r="C27" s="1">
         <v>22</v>
       </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
       <c r="E27" s="1" t="s">
         <v>32</v>
       </c>
@@ -1591,13 +1655,16 @@
         <v>8</v>
       </c>
       <c r="H27" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
       <c r="C28" s="1">
         <v>23</v>
       </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
       <c r="E28" s="1" t="s">
         <v>33</v>
       </c>
@@ -1608,13 +1675,16 @@
         <v>8</v>
       </c>
       <c r="H28" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
       <c r="C29" s="1">
         <v>24</v>
       </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
       <c r="E29" s="1" t="s">
         <v>34</v>
       </c>
@@ -1625,13 +1695,16 @@
         <v>8</v>
       </c>
       <c r="H29" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="1">
         <v>25</v>
       </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
       <c r="E30" s="1" t="s">
         <v>35</v>
       </c>
@@ -1642,13 +1715,16 @@
         <v>9</v>
       </c>
       <c r="H30" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="1">
         <v>26</v>
       </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
       <c r="E31" s="1" t="s">
         <v>36</v>
       </c>
@@ -1659,13 +1735,16 @@
         <v>9</v>
       </c>
       <c r="H31" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="1">
         <v>27</v>
       </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
       <c r="E32" s="1" t="s">
         <v>37</v>
       </c>
@@ -1676,13 +1755,16 @@
         <v>9</v>
       </c>
       <c r="H32" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="1">
         <v>28</v>
       </c>
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
       <c r="E33" s="1" t="s">
         <v>38</v>
       </c>
@@ -1693,13 +1775,16 @@
         <v>10</v>
       </c>
       <c r="H33" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="1">
         <v>29</v>
       </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
       <c r="E34" s="1" t="s">
         <v>39</v>
       </c>
@@ -1710,13 +1795,16 @@
         <v>10</v>
       </c>
       <c r="H34" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="1">
         <v>30</v>
       </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
       <c r="E35" s="1" t="s">
         <v>40</v>
       </c>
@@ -1727,13 +1815,16 @@
         <v>10</v>
       </c>
       <c r="H35" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="1">
         <v>31</v>
       </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
       <c r="E36" s="1" t="s">
         <v>41</v>
       </c>
@@ -1744,13 +1835,16 @@
         <v>11</v>
       </c>
       <c r="H36" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="1">
         <v>32</v>
       </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
       <c r="E37" s="1" t="s">
         <v>42</v>
       </c>
@@ -1761,13 +1855,16 @@
         <v>11</v>
       </c>
       <c r="H37" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="1">
         <v>33</v>
       </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
       <c r="E38" s="1" t="s">
         <v>43</v>
       </c>
@@ -1778,13 +1875,16 @@
         <v>11</v>
       </c>
       <c r="H38" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="1">
         <v>34</v>
       </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
       <c r="E39" s="1" t="s">
         <v>44</v>
       </c>
@@ -1795,13 +1895,16 @@
         <v>12</v>
       </c>
       <c r="H39" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="1">
         <v>35</v>
       </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
       <c r="E40" s="1" t="s">
         <v>45</v>
       </c>
@@ -1812,13 +1915,16 @@
         <v>12</v>
       </c>
       <c r="H40" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="1">
         <v>36</v>
       </c>
+      <c r="D41" s="1">
+        <v>3</v>
+      </c>
       <c r="E41" s="1" t="s">
         <v>46</v>
       </c>
@@ -1829,7 +1935,7 @@
         <v>12</v>
       </c>
       <c r="H41" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -62,13 +62,13 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>0级战装</t>
-  </si>
-  <si>
-    <t>0级法装</t>
-  </si>
-  <si>
-    <t>0级道装</t>
+    <t>1级战装</t>
+  </si>
+  <si>
+    <t>1级法装</t>
+  </si>
+  <si>
+    <t>1级道装</t>
   </si>
   <si>
     <t>10级战装</t>
@@ -1703,7 +1703,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>35</v>
@@ -1723,7 +1723,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>36</v>
@@ -1743,7 +1743,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>37</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -41,10 +41,10 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AttrIdList</t>
-  </si>
-  <si>
-    <t>AttrValueList</t>
+    <t>AtrIdList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
   </si>
   <si>
     <t>Count</t>
@@ -65,15 +65,30 @@
     <t>1级战装</t>
   </si>
   <si>
+    <t>1007,91</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
     <t>1级法装</t>
   </si>
   <si>
+    <t>1008,91</t>
+  </si>
+  <si>
     <t>1级道装</t>
   </si>
   <si>
+    <t>1009,91</t>
+  </si>
+  <si>
     <t>10级战装</t>
   </si>
   <si>
+    <t>2,1</t>
+  </si>
+  <si>
     <t>10级法装</t>
   </si>
   <si>
@@ -83,6 +98,9 @@
     <t>20级战装</t>
   </si>
   <si>
+    <t>3,1</t>
+  </si>
+  <si>
     <t>20级法装</t>
   </si>
   <si>
@@ -92,6 +110,9 @@
     <t>30级战装</t>
   </si>
   <si>
+    <t>4,1</t>
+  </si>
+  <si>
     <t>30级法装</t>
   </si>
   <si>
@@ -101,6 +122,9 @@
     <t>40级战装</t>
   </si>
   <si>
+    <t>5,1</t>
+  </si>
+  <si>
     <t>40级法装</t>
   </si>
   <si>
@@ -110,6 +134,9 @@
     <t>50级战装</t>
   </si>
   <si>
+    <t>6,1</t>
+  </si>
+  <si>
     <t>50级法装</t>
   </si>
   <si>
@@ -119,6 +146,9 @@
     <t>60级战装</t>
   </si>
   <si>
+    <t>7,1</t>
+  </si>
+  <si>
     <t>60级法装</t>
   </si>
   <si>
@@ -128,6 +158,9 @@
     <t>70级战装</t>
   </si>
   <si>
+    <t>8,1</t>
+  </si>
+  <si>
     <t>70级法装</t>
   </si>
   <si>
@@ -137,6 +170,9 @@
     <t>80级战装</t>
   </si>
   <si>
+    <t>9,1</t>
+  </si>
+  <si>
     <t>80级法装</t>
   </si>
   <si>
@@ -146,6 +182,9 @@
     <t>90级战装</t>
   </si>
   <si>
+    <t>10,1</t>
+  </si>
+  <si>
     <t>90级法装</t>
   </si>
   <si>
@@ -155,6 +194,9 @@
     <t>100级战装</t>
   </si>
   <si>
+    <t>11,1</t>
+  </si>
+  <si>
     <t>100级法装</t>
   </si>
   <si>
@@ -162,6 +204,9 @@
   </si>
   <si>
     <t>110级战装</t>
+  </si>
+  <si>
+    <t>12,1</t>
   </si>
   <si>
     <t>110级法装</t>
@@ -808,6 +853,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1228,11 +1274,11 @@
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
+      <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="H6" s="1">
         <v>8</v>
@@ -1246,13 +1292,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="H7" s="1">
         <v>8</v>
@@ -1266,13 +1312,13 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
       </c>
       <c r="H8" s="1">
         <v>8</v>
@@ -1286,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G9" s="1">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -1306,13 +1352,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G10" s="1">
-        <v>2</v>
+      <c r="G10" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H10" s="1">
         <v>8</v>
@@ -1326,13 +1372,13 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G11" s="1">
-        <v>2</v>
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H11" s="1">
         <v>8</v>
@@ -1346,13 +1392,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G12" s="1">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="H12" s="1">
         <v>8</v>
@@ -1366,13 +1412,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G13" s="1">
-        <v>3</v>
+        <v>24</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="H13" s="1">
         <v>8</v>
@@ -1386,13 +1432,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G14" s="1">
-        <v>3</v>
+        <v>25</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="H14" s="1">
         <v>8</v>
@@ -1406,13 +1452,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G15" s="1">
-        <v>4</v>
+        <v>26</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="H15" s="1">
         <v>8</v>
@@ -1426,13 +1472,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G16" s="1">
-        <v>4</v>
+        <v>28</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="H16" s="1">
         <v>8</v>
@@ -1446,13 +1492,13 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G17" s="1">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="H17" s="1">
         <v>8</v>
@@ -1466,13 +1512,13 @@
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G18" s="1">
-        <v>5</v>
+        <v>30</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="H18" s="1">
         <v>8</v>
@@ -1486,13 +1532,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G19" s="1">
-        <v>5</v>
+        <v>32</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="H19" s="1">
         <v>8</v>
@@ -1506,13 +1552,13 @@
         <v>2</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G20" s="1">
-        <v>5</v>
+        <v>33</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="H20" s="1">
         <v>8</v>
@@ -1526,13 +1572,13 @@
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G21" s="1">
-        <v>6</v>
+        <v>34</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="H21" s="1">
         <v>8</v>
@@ -1546,13 +1592,13 @@
         <v>2</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G22" s="1">
-        <v>6</v>
+        <v>36</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="H22" s="1">
         <v>8</v>
@@ -1566,13 +1612,13 @@
         <v>2</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G23" s="1">
-        <v>6</v>
+        <v>37</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="H23" s="1">
         <v>8</v>
@@ -1586,13 +1632,13 @@
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G24" s="1">
-        <v>7</v>
+        <v>38</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="H24" s="1">
         <v>8</v>
@@ -1606,13 +1652,13 @@
         <v>2</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G25" s="1">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="H25" s="1">
         <v>8</v>
@@ -1626,13 +1672,13 @@
         <v>2</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G26" s="1">
-        <v>7</v>
+        <v>41</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="H26" s="1">
         <v>8</v>
@@ -1646,13 +1692,13 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G27" s="1">
-        <v>8</v>
+        <v>42</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="H27" s="1">
         <v>8</v>
@@ -1666,13 +1712,13 @@
         <v>2</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G28" s="1">
-        <v>8</v>
+        <v>44</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="H28" s="1">
         <v>8</v>
@@ -1686,13 +1732,13 @@
         <v>2</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G29" s="1">
-        <v>8</v>
+        <v>45</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="H29" s="1">
         <v>8</v>
@@ -1706,13 +1752,13 @@
         <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G30" s="1">
-        <v>9</v>
+        <v>46</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="H30" s="1">
         <v>8</v>
@@ -1726,13 +1772,13 @@
         <v>3</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G31" s="1">
-        <v>9</v>
+        <v>48</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="H31" s="1">
         <v>8</v>
@@ -1746,13 +1792,13 @@
         <v>3</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G32" s="1">
-        <v>9</v>
+        <v>49</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="H32" s="1">
         <v>8</v>
@@ -1766,13 +1812,13 @@
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G33" s="1">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="H33" s="1">
         <v>8</v>
@@ -1786,13 +1832,13 @@
         <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G34" s="1">
-        <v>10</v>
+        <v>52</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="H34" s="1">
         <v>8</v>
@@ -1806,13 +1852,13 @@
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G35" s="1">
-        <v>10</v>
+        <v>53</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="H35" s="1">
         <v>8</v>
@@ -1826,13 +1872,13 @@
         <v>3</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F36" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G36" s="1">
-        <v>11</v>
+        <v>54</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="H36" s="1">
         <v>8</v>
@@ -1846,13 +1892,13 @@
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G37" s="1">
-        <v>11</v>
+        <v>56</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="H37" s="1">
         <v>8</v>
@@ -1866,13 +1912,13 @@
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G38" s="1">
-        <v>11</v>
+        <v>57</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="H38" s="1">
         <v>8</v>
@@ -1886,13 +1932,13 @@
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="1">
-        <v>1007</v>
-      </c>
-      <c r="G39" s="1">
+        <v>58</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="H39" s="1">
         <v>8</v>
@@ -1906,13 +1952,13 @@
         <v>3</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F40" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G40" s="1">
-        <v>12</v>
+        <v>60</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="H40" s="1">
         <v>8</v>
@@ -1926,13 +1972,13 @@
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F41" s="1">
-        <v>1009</v>
-      </c>
-      <c r="G41" s="1">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="H41" s="1">
         <v>8</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="定制配置" sheetId="2" r:id="rId1"/>
+    <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
+    <sheet name="宠物图鉴" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="78">
   <si>
     <t>#</t>
   </si>
@@ -213,6 +214,54 @@
   </si>
   <si>
     <t>110级道装</t>
+  </si>
+  <si>
+    <t>落日平原</t>
+  </si>
+  <si>
+    <t>幽暗沼泽</t>
+  </si>
+  <si>
+    <t>碎石矿场</t>
+  </si>
+  <si>
+    <t>枯骨荒漠</t>
+  </si>
+  <si>
+    <t>迷雾森林</t>
+  </si>
+  <si>
+    <t>熔火地穴</t>
+  </si>
+  <si>
+    <t>雷光废墟</t>
+  </si>
+  <si>
+    <t>冰封王陵</t>
+  </si>
+  <si>
+    <t>诅咒祭坛</t>
+  </si>
+  <si>
+    <t>13,1</t>
+  </si>
+  <si>
+    <t>虚空裂谷</t>
+  </si>
+  <si>
+    <t>14,1</t>
+  </si>
+  <si>
+    <t>龙眠之地</t>
+  </si>
+  <si>
+    <t>15,1</t>
+  </si>
+  <si>
+    <t>永恒神界</t>
+  </si>
+  <si>
+    <t>16,1</t>
   </si>
 </sst>
 </file>
@@ -225,7 +274,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +296,12 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -717,142 +772,143 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1274,10 +1330,10 @@
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="1">
@@ -1294,10 +1350,10 @@
       <c r="E7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="1">
@@ -1314,10 +1370,10 @@
       <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="1">
@@ -1334,10 +1390,10 @@
       <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="1">
@@ -1354,10 +1410,10 @@
       <c r="E10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H10" s="1">
@@ -1374,10 +1430,10 @@
       <c r="E11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="1">
@@ -1394,10 +1450,10 @@
       <c r="E12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="1">
@@ -1414,10 +1470,10 @@
       <c r="E13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="1">
@@ -1434,10 +1490,10 @@
       <c r="E14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="1">
@@ -1454,10 +1510,10 @@
       <c r="E15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H15" s="1">
@@ -1474,10 +1530,10 @@
       <c r="E16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="1">
@@ -1494,10 +1550,10 @@
       <c r="E17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H17" s="1">
@@ -1514,10 +1570,10 @@
       <c r="E18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H18" s="1">
@@ -1534,10 +1590,10 @@
       <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H19" s="1">
@@ -1554,10 +1610,10 @@
       <c r="E20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H20" s="1">
@@ -1574,10 +1630,10 @@
       <c r="E21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H21" s="1">
@@ -1594,10 +1650,10 @@
       <c r="E22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H22" s="1">
@@ -1614,10 +1670,10 @@
       <c r="E23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H23" s="1">
@@ -1634,10 +1690,10 @@
       <c r="E24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H24" s="1">
@@ -1654,10 +1710,10 @@
       <c r="E25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H25" s="1">
@@ -1674,10 +1730,10 @@
       <c r="E26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H26" s="1">
@@ -1694,10 +1750,10 @@
       <c r="E27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="4" t="s">
         <v>43</v>
       </c>
       <c r="H27" s="1">
@@ -1714,10 +1770,10 @@
       <c r="E28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="4" t="s">
         <v>43</v>
       </c>
       <c r="H28" s="1">
@@ -1734,10 +1790,10 @@
       <c r="E29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="4" t="s">
         <v>43</v>
       </c>
       <c r="H29" s="1">
@@ -1754,10 +1810,10 @@
       <c r="E30" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="4" t="s">
         <v>47</v>
       </c>
       <c r="H30" s="1">
@@ -1774,10 +1830,10 @@
       <c r="E31" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="4" t="s">
         <v>47</v>
       </c>
       <c r="H31" s="1">
@@ -1794,10 +1850,10 @@
       <c r="E32" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="4" t="s">
         <v>47</v>
       </c>
       <c r="H32" s="1">
@@ -1814,10 +1870,10 @@
       <c r="E33" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H33" s="1">
@@ -1834,10 +1890,10 @@
       <c r="E34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H34" s="1">
@@ -1854,10 +1910,10 @@
       <c r="E35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H35" s="1">
@@ -1874,10 +1930,10 @@
       <c r="E36" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H36" s="1">
@@ -1894,10 +1950,10 @@
       <c r="E37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H37" s="1">
@@ -1914,10 +1970,10 @@
       <c r="E38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H38" s="1">
@@ -1934,10 +1990,10 @@
       <c r="E39" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H39" s="1">
@@ -1954,10 +2010,10 @@
       <c r="E40" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H40" s="1">
@@ -1974,14 +2030,359 @@
       <c r="E41" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H41" s="1">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:I17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="15.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.9166666666667" style="1" customWidth="1"/>
+    <col min="7" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.9166666666667" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C6" s="1">
+        <v>1101</v>
+      </c>
+      <c r="D6" s="1">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C7" s="1">
+        <v>1102</v>
+      </c>
+      <c r="D7" s="1">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C8" s="1">
+        <v>1103</v>
+      </c>
+      <c r="D8" s="1">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C9" s="1">
+        <v>1104</v>
+      </c>
+      <c r="D9" s="1">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C10" s="1">
+        <v>1105</v>
+      </c>
+      <c r="D10" s="1">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C11" s="1">
+        <v>1106</v>
+      </c>
+      <c r="D11" s="1">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C12" s="1">
+        <v>1107</v>
+      </c>
+      <c r="D12" s="1">
+        <v>11</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C13" s="1">
+        <v>1108</v>
+      </c>
+      <c r="D13" s="1">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C14" s="1">
+        <v>1109</v>
+      </c>
+      <c r="D14" s="1">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C15" s="1">
+        <v>1110</v>
+      </c>
+      <c r="D15" s="1">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C16" s="1">
+        <v>1111</v>
+      </c>
+      <c r="D16" s="1">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C17" s="1">
+        <v>1112</v>
+      </c>
+      <c r="D17" s="1">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="1">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="79">
   <si>
     <t>#</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>落日平原</t>
+  </si>
+  <si>
+    <t>27,91</t>
   </si>
   <si>
     <t>幽暗沼泽</t>
@@ -2156,7 +2159,7 @@
         <v>62</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>31</v>
@@ -2173,10 +2176,10 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>35</v>
@@ -2193,10 +2196,10 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>39</v>
@@ -2213,10 +2216,10 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>43</v>
@@ -2233,10 +2236,10 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>47</v>
@@ -2253,10 +2256,10 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>51</v>
@@ -2273,10 +2276,10 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>55</v>
@@ -2293,10 +2296,10 @@
         <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>59</v>
@@ -2313,13 +2316,13 @@
         <v>11</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H14" s="1">
         <v>6</v>
@@ -2333,13 +2336,13 @@
         <v>11</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H15" s="1">
         <v>6</v>
@@ -2353,13 +2356,13 @@
         <v>11</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16" s="1">
         <v>6</v>
@@ -2373,13 +2376,13 @@
         <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" s="1">
         <v>6</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="95">
   <si>
     <t>#</t>
   </si>
@@ -42,6 +42,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>LogoId</t>
+  </si>
+  <si>
     <t>AtrIdList</t>
   </si>
   <si>
@@ -66,6 +69,9 @@
     <t>1级战装</t>
   </si>
   <si>
+    <t>Bag/Equip/Box_Equip_1_1</t>
+  </si>
+  <si>
     <t>1007,91</t>
   </si>
   <si>
@@ -75,12 +81,18 @@
     <t>1级法装</t>
   </si>
   <si>
+    <t>Bag/Equip/Box_Equip_2_1</t>
+  </si>
+  <si>
     <t>1008,91</t>
   </si>
   <si>
     <t>1级道装</t>
   </si>
   <si>
+    <t>Bag/Equip/Box_Equip_3_1</t>
+  </si>
+  <si>
     <t>1009,91</t>
   </si>
   <si>
@@ -219,49 +231,85 @@
     <t>落日平原</t>
   </si>
   <si>
+    <t>Player/Boss/Boss1</t>
+  </si>
+  <si>
     <t>27,91</t>
   </si>
   <si>
     <t>幽暗沼泽</t>
   </si>
   <si>
+    <t>Player/Boss/Boss2</t>
+  </si>
+  <si>
     <t>碎石矿场</t>
   </si>
   <si>
+    <t>Player/Boss/Boss3</t>
+  </si>
+  <si>
     <t>枯骨荒漠</t>
   </si>
   <si>
+    <t>Player/Boss/Boss4</t>
+  </si>
+  <si>
     <t>迷雾森林</t>
   </si>
   <si>
+    <t>Player/Boss/Boss5</t>
+  </si>
+  <si>
     <t>熔火地穴</t>
   </si>
   <si>
+    <t>Player/Boss/Boss6</t>
+  </si>
+  <si>
     <t>雷光废墟</t>
   </si>
   <si>
+    <t>Player/Boss/Boss7</t>
+  </si>
+  <si>
     <t>冰封王陵</t>
   </si>
   <si>
+    <t>Player/Boss/Boss8</t>
+  </si>
+  <si>
     <t>诅咒祭坛</t>
   </si>
   <si>
+    <t>Player/Boss/Boss9</t>
+  </si>
+  <si>
     <t>13,1</t>
   </si>
   <si>
     <t>虚空裂谷</t>
   </si>
   <si>
+    <t>Player/Boss/Boss10</t>
+  </si>
+  <si>
     <t>14,1</t>
   </si>
   <si>
     <t>龙眠之地</t>
   </si>
   <si>
+    <t>Player/Boss/Boss11</t>
+  </si>
+  <si>
     <t>15,1</t>
   </si>
   <si>
     <t>永恒神界</t>
+  </si>
+  <si>
+    <t>Player/Boss/Boss12</t>
   </si>
   <si>
     <t>16,1</t>
@@ -277,7 +325,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +341,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
@@ -301,6 +355,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -775,143 +830,146 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1232,98 +1290,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:I41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="15.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.9166666666667" style="1" customWidth="1"/>
-    <col min="7" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.9166666666667" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="21.1666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.9166666666667" style="1" customWidth="1"/>
+    <col min="8" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.9166666666667" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:9">
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:9">
-      <c r="I2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C3" s="2" t="s">
+    <row r="1" customHeight="1" spans="3:10">
+      <c r="F1" s="2"/>
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:10">
+      <c r="F2" s="2"/>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C4" s="2" t="s">
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="G5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="J5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1331,19 +1401,22 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="G6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1351,19 +1424,22 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="I7" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1371,19 +1447,22 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:9">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1391,19 +1470,22 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:9">
+        <v>22</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1411,19 +1493,22 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:9">
+        <v>24</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1431,19 +1516,22 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:9">
+      <c r="H11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1451,19 +1539,22 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:9">
+        <v>26</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1471,19 +1562,22 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:9">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1491,19 +1585,22 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:9">
+        <v>29</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1511,19 +1608,22 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:9">
+        <v>30</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1531,19 +1631,22 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:8">
+        <v>32</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:9">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1551,19 +1654,28 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:8">
+        <v>33</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:9">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1571,19 +1683,28 @@
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:8">
+        <v>34</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:9">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1591,19 +1712,28 @@
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:8">
+        <v>36</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1611,19 +1741,28 @@
         <v>2</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:8">
+        <v>37</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:9">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1631,19 +1770,28 @@
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:8">
+        <v>38</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:9">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -1651,19 +1799,28 @@
         <v>2</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:8">
+        <v>40</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:9">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -1671,19 +1828,28 @@
         <v>2</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:8">
+        <v>41</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:9">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -1691,19 +1857,28 @@
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:8">
+        <v>42</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:9">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -1711,19 +1886,28 @@
         <v>2</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H25" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:8">
+        <v>44</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:9">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -1731,19 +1915,28 @@
         <v>2</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H26" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:8">
+        <v>45</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:9">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -1751,19 +1944,28 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:8">
+        <v>46</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:9">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -1771,19 +1973,28 @@
         <v>2</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:8">
+        <v>48</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:9">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -1791,19 +2002,28 @@
         <v>2</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H29" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:8">
+        <v>49</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:9">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -1811,19 +2031,28 @@
         <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H30" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:8">
+        <v>50</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -1831,19 +2060,28 @@
         <v>3</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H31" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:8">
+        <v>52</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C32" s="1">
         <v>27</v>
       </c>
@@ -1851,19 +2089,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H32" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:8">
+        <v>53</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:9">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -1871,19 +2118,28 @@
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H33" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:8">
+        <v>54</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I33" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:9">
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -1891,19 +2147,28 @@
         <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H34" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:8">
+        <v>56</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I34" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:9">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -1911,19 +2176,28 @@
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H35" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:8">
+        <v>57</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I35" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:9">
+      <c r="A36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -1931,19 +2205,28 @@
         <v>3</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H36" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:8">
+        <v>58</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I36" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:9">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C37" s="1">
         <v>32</v>
       </c>
@@ -1951,19 +2234,28 @@
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H37" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:8">
+        <v>60</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I37" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:9">
+      <c r="A38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C38" s="1">
         <v>33</v>
       </c>
@@ -1971,19 +2263,28 @@
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H38" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:8">
+        <v>61</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I38" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:9">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C39" s="1">
         <v>34</v>
       </c>
@@ -1991,19 +2292,28 @@
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H39" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:8">
+        <v>62</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I39" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:9">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C40" s="1">
         <v>35</v>
       </c>
@@ -2011,19 +2321,28 @@
         <v>3</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H40" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:8">
+        <v>64</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I40" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:9">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C41" s="1">
         <v>36</v>
       </c>
@@ -2031,21 +2350,24 @@
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H41" s="1">
+        <v>65</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I41" s="1">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:F5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2057,340 +2379,432 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:I17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="15.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.9166666666667" style="1" customWidth="1"/>
-    <col min="7" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.9166666666667" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="5" max="6" width="15.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.9166666666667" style="1" customWidth="1"/>
+    <col min="8" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.9166666666667" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="I2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C3" s="2" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="F1" s="2"/>
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="F2" s="2"/>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C4" s="2" t="s">
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="G5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="J5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1101</v>
       </c>
       <c r="D6" s="1">
         <v>11</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="E6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>1102</v>
       </c>
       <c r="D7" s="1">
         <v>11</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="E7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>1103</v>
       </c>
       <c r="D8" s="1">
         <v>11</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="E8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C9" s="1">
         <v>1104</v>
       </c>
       <c r="D9" s="1">
         <v>11</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="E9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C10" s="1">
         <v>1105</v>
       </c>
       <c r="D10" s="1">
         <v>11</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="E10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C11" s="1">
         <v>1106</v>
       </c>
       <c r="D11" s="1">
         <v>11</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="H11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C12" s="1">
         <v>1107</v>
       </c>
       <c r="D12" s="1">
         <v>11</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="E12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C13" s="1">
         <v>1108</v>
       </c>
       <c r="D13" s="1">
         <v>11</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C14" s="1">
         <v>1109</v>
       </c>
       <c r="D14" s="1">
         <v>11</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="E14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C15" s="1">
         <v>1110</v>
       </c>
       <c r="D15" s="1">
         <v>11</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="E15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C16" s="1">
         <v>1111</v>
       </c>
       <c r="D16" s="1">
         <v>11</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="E16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C17" s="1">
         <v>1112</v>
       </c>
       <c r="D17" s="1">
         <v>11</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="E17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="I17" s="1">
         <v>6</v>
       </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:9">
+      <c r="F18" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:F5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="102">
   <si>
     <t>#</t>
   </si>
@@ -111,7 +111,7 @@
     <t>20级战装</t>
   </si>
   <si>
-    <t>3,1</t>
+    <t>3,2</t>
   </si>
   <si>
     <t>20级法装</t>
@@ -123,7 +123,7 @@
     <t>30级战装</t>
   </si>
   <si>
-    <t>4,1</t>
+    <t>4,2</t>
   </si>
   <si>
     <t>30级法装</t>
@@ -135,7 +135,7 @@
     <t>40级战装</t>
   </si>
   <si>
-    <t>5,1</t>
+    <t>5,3</t>
   </si>
   <si>
     <t>40级法装</t>
@@ -147,7 +147,7 @@
     <t>50级战装</t>
   </si>
   <si>
-    <t>6,1</t>
+    <t>6,3</t>
   </si>
   <si>
     <t>50级法装</t>
@@ -159,7 +159,7 @@
     <t>60级战装</t>
   </si>
   <si>
-    <t>7,1</t>
+    <t>7,4</t>
   </si>
   <si>
     <t>60级法装</t>
@@ -171,7 +171,7 @@
     <t>70级战装</t>
   </si>
   <si>
-    <t>8,1</t>
+    <t>8,4</t>
   </si>
   <si>
     <t>70级法装</t>
@@ -183,7 +183,7 @@
     <t>80级战装</t>
   </si>
   <si>
-    <t>9,1</t>
+    <t>9,5</t>
   </si>
   <si>
     <t>80级法装</t>
@@ -195,7 +195,7 @@
     <t>90级战装</t>
   </si>
   <si>
-    <t>10,1</t>
+    <t>10,5</t>
   </si>
   <si>
     <t>90级法装</t>
@@ -207,7 +207,7 @@
     <t>100级战装</t>
   </si>
   <si>
-    <t>11,1</t>
+    <t>11,6</t>
   </si>
   <si>
     <t>100级法装</t>
@@ -219,7 +219,7 @@
     <t>110级战装</t>
   </si>
   <si>
-    <t>12,1</t>
+    <t>12,6</t>
   </si>
   <si>
     <t>110级法装</t>
@@ -243,49 +243,70 @@
     <t>Player/Boss/Boss2</t>
   </si>
   <si>
+    <t>6,4</t>
+  </si>
+  <si>
     <t>碎石矿场</t>
   </si>
   <si>
     <t>Player/Boss/Boss3</t>
   </si>
   <si>
+    <t>7,5</t>
+  </si>
+  <si>
     <t>枯骨荒漠</t>
   </si>
   <si>
     <t>Player/Boss/Boss4</t>
   </si>
   <si>
+    <t>8,6</t>
+  </si>
+  <si>
     <t>迷雾森林</t>
   </si>
   <si>
     <t>Player/Boss/Boss5</t>
   </si>
   <si>
+    <t>9,7</t>
+  </si>
+  <si>
     <t>熔火地穴</t>
   </si>
   <si>
     <t>Player/Boss/Boss6</t>
   </si>
   <si>
+    <t>10,8</t>
+  </si>
+  <si>
     <t>雷光废墟</t>
   </si>
   <si>
     <t>Player/Boss/Boss7</t>
   </si>
   <si>
+    <t>11,9</t>
+  </si>
+  <si>
     <t>冰封王陵</t>
   </si>
   <si>
     <t>Player/Boss/Boss8</t>
   </si>
   <si>
+    <t>12,10</t>
+  </si>
+  <si>
     <t>诅咒祭坛</t>
   </si>
   <si>
     <t>Player/Boss/Boss9</t>
   </si>
   <si>
-    <t>13,1</t>
+    <t>13,11</t>
   </si>
   <si>
     <t>虚空裂谷</t>
@@ -294,7 +315,7 @@
     <t>Player/Boss/Boss10</t>
   </si>
   <si>
-    <t>14,1</t>
+    <t>14,12</t>
   </si>
   <si>
     <t>龙眠之地</t>
@@ -303,7 +324,7 @@
     <t>Player/Boss/Boss11</t>
   </si>
   <si>
-    <t>15,1</t>
+    <t>15,13</t>
   </si>
   <si>
     <t>永恒神界</t>
@@ -312,7 +333,7 @@
     <t>Player/Boss/Boss12</t>
   </si>
   <si>
-    <t>16,1</t>
+    <t>16,14</t>
   </si>
 </sst>
 </file>
@@ -2367,7 +2388,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:F5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2521,7 +2542,7 @@
         <v>68</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="I7" s="1">
         <v>6</v>
@@ -2535,16 +2556,16 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="I8" s="1">
         <v>6</v>
@@ -2558,16 +2579,16 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>
@@ -2581,16 +2602,16 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="I10" s="1">
         <v>6</v>
@@ -2610,16 +2631,16 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I11" s="1">
         <v>6</v>
@@ -2639,16 +2660,16 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="I12" s="1">
         <v>6</v>
@@ -2668,16 +2689,16 @@
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="I13" s="1">
         <v>6</v>
@@ -2697,16 +2718,16 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I14" s="1">
         <v>6</v>
@@ -2726,16 +2747,16 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I15" s="1">
         <v>6</v>
@@ -2755,16 +2776,16 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I16" s="1">
         <v>6</v>
@@ -2784,16 +2805,16 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="I17" s="1">
         <v>6</v>
@@ -2804,7 +2825,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:F5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="118">
   <si>
     <t>#</t>
   </si>
@@ -51,7 +51,16 @@
     <t>AtrVueList</t>
   </si>
   <si>
-    <t>Count</t>
+    <t>SpeAtrId</t>
+  </si>
+  <si>
+    <t>SpeAtrVue</t>
+  </si>
+  <si>
+    <t>BaseFee</t>
+  </si>
+  <si>
+    <t>MaxLevel</t>
   </si>
   <si>
     <t>Des</t>
@@ -66,175 +75,232 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>1级战装</t>
+    <t>1级武器</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_1_1</t>
   </si>
   <si>
-    <t>1007,91</t>
+    <t>3,91</t>
+  </si>
+  <si>
+    <t>10,1</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>1级衣服</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_2</t>
+  </si>
+  <si>
+    <t>2,91</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>1级首饰</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_3</t>
+  </si>
+  <si>
+    <t>1,91</t>
+  </si>
+  <si>
+    <t>200,1</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>10级武器</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_2_1</t>
+  </si>
+  <si>
+    <t>20,1</t>
+  </si>
+  <si>
+    <t>10级衣服</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_2_2</t>
+  </si>
+  <si>
+    <t>10级首饰</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_2_3</t>
+  </si>
+  <si>
+    <t>400,1</t>
+  </si>
+  <si>
+    <t>20级武器</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_3_1</t>
+  </si>
+  <si>
+    <t>30,1</t>
+  </si>
+  <si>
+    <t>20级衣服</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_3_2</t>
+  </si>
+  <si>
+    <t>20级首饰</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_3_3</t>
+  </si>
+  <si>
+    <t>600,1</t>
+  </si>
+  <si>
+    <t>30级武器</t>
+  </si>
+  <si>
+    <t>40,1</t>
+  </si>
+  <si>
+    <t>30级衣服</t>
+  </si>
+  <si>
+    <t>30级首饰</t>
+  </si>
+  <si>
+    <t>800,1</t>
+  </si>
+  <si>
+    <t>40级武器</t>
+  </si>
+  <si>
+    <t>50,1</t>
+  </si>
+  <si>
+    <t>40级衣服</t>
+  </si>
+  <si>
+    <t>40级首饰</t>
+  </si>
+  <si>
+    <t>1000,1</t>
+  </si>
+  <si>
+    <t>50级武器</t>
+  </si>
+  <si>
+    <t>60,1</t>
+  </si>
+  <si>
+    <t>50级衣服</t>
+  </si>
+  <si>
+    <t>50级首饰</t>
+  </si>
+  <si>
+    <t>1200,1</t>
+  </si>
+  <si>
+    <t>60级武器</t>
+  </si>
+  <si>
+    <t>70,1</t>
+  </si>
+  <si>
+    <t>60级衣服</t>
+  </si>
+  <si>
+    <t>60级首饰</t>
+  </si>
+  <si>
+    <t>1400,1</t>
+  </si>
+  <si>
+    <t>70级武器</t>
+  </si>
+  <si>
+    <t>8,4</t>
+  </si>
+  <si>
+    <t>70级衣服</t>
+  </si>
+  <si>
+    <t>70级首饰</t>
+  </si>
+  <si>
+    <t>80级武器</t>
+  </si>
+  <si>
+    <t>9,5</t>
+  </si>
+  <si>
+    <t>80级衣服</t>
+  </si>
+  <si>
+    <t>80级首饰</t>
+  </si>
+  <si>
+    <t>90级武器</t>
+  </si>
+  <si>
+    <t>10,5</t>
+  </si>
+  <si>
+    <t>90级衣服</t>
+  </si>
+  <si>
+    <t>90级首饰</t>
+  </si>
+  <si>
+    <t>100级武器</t>
+  </si>
+  <si>
+    <t>11,6</t>
+  </si>
+  <si>
+    <t>100级衣服</t>
+  </si>
+  <si>
+    <t>100级首饰</t>
+  </si>
+  <si>
+    <t>110级武器</t>
+  </si>
+  <si>
+    <t>12,6</t>
+  </si>
+  <si>
+    <t>110级衣服</t>
+  </si>
+  <si>
+    <t>110级首饰</t>
+  </si>
+  <si>
+    <t>落日平原</t>
+  </si>
+  <si>
+    <t>Player/Boss/Boss1</t>
+  </si>
+  <si>
+    <t>27,91</t>
   </si>
   <si>
     <t>1,1</t>
   </si>
   <si>
-    <t>1级法装</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_2_1</t>
-  </si>
-  <si>
-    <t>1008,91</t>
-  </si>
-  <si>
-    <t>1级道装</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_3_1</t>
-  </si>
-  <si>
-    <t>1009,91</t>
-  </si>
-  <si>
-    <t>10级战装</t>
-  </si>
-  <si>
-    <t>2,1</t>
-  </si>
-  <si>
-    <t>10级法装</t>
-  </si>
-  <si>
-    <t>10级道装</t>
-  </si>
-  <si>
-    <t>20级战装</t>
-  </si>
-  <si>
-    <t>3,2</t>
-  </si>
-  <si>
-    <t>20级法装</t>
-  </si>
-  <si>
-    <t>20级道装</t>
-  </si>
-  <si>
-    <t>30级战装</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>30级法装</t>
-  </si>
-  <si>
-    <t>30级道装</t>
-  </si>
-  <si>
-    <t>40级战装</t>
-  </si>
-  <si>
-    <t>5,3</t>
-  </si>
-  <si>
-    <t>40级法装</t>
-  </si>
-  <si>
-    <t>40级道装</t>
-  </si>
-  <si>
-    <t>50级战装</t>
-  </si>
-  <si>
-    <t>6,3</t>
-  </si>
-  <si>
-    <t>50级法装</t>
-  </si>
-  <si>
-    <t>50级道装</t>
-  </si>
-  <si>
-    <t>60级战装</t>
-  </si>
-  <si>
-    <t>7,4</t>
-  </si>
-  <si>
-    <t>60级法装</t>
-  </si>
-  <si>
-    <t>60级道装</t>
-  </si>
-  <si>
-    <t>70级战装</t>
-  </si>
-  <si>
-    <t>8,4</t>
-  </si>
-  <si>
-    <t>70级法装</t>
-  </si>
-  <si>
-    <t>70级道装</t>
-  </si>
-  <si>
-    <t>80级战装</t>
-  </si>
-  <si>
-    <t>9,5</t>
-  </si>
-  <si>
-    <t>80级法装</t>
-  </si>
-  <si>
-    <t>80级道装</t>
-  </si>
-  <si>
-    <t>90级战装</t>
-  </si>
-  <si>
-    <t>10,5</t>
-  </si>
-  <si>
-    <t>90级法装</t>
-  </si>
-  <si>
-    <t>90级道装</t>
-  </si>
-  <si>
-    <t>100级战装</t>
-  </si>
-  <si>
-    <t>11,6</t>
-  </si>
-  <si>
-    <t>100级法装</t>
-  </si>
-  <si>
-    <t>100级道装</t>
-  </si>
-  <si>
-    <t>110级战装</t>
-  </si>
-  <si>
-    <t>12,6</t>
-  </si>
-  <si>
-    <t>110级法装</t>
-  </si>
-  <si>
-    <t>110级道装</t>
-  </si>
-  <si>
-    <t>落日平原</t>
-  </si>
-  <si>
-    <t>Player/Boss/Boss1</t>
-  </si>
-  <si>
-    <t>27,91</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>暴击</t>
   </si>
   <si>
     <t>幽暗沼泽</t>
@@ -243,7 +309,7 @@
     <t>Player/Boss/Boss2</t>
   </si>
   <si>
-    <t>6,4</t>
+    <t>爆伤</t>
   </si>
   <si>
     <t>碎石矿场</t>
@@ -252,7 +318,7 @@
     <t>Player/Boss/Boss3</t>
   </si>
   <si>
-    <t>7,5</t>
+    <t>冷却</t>
   </si>
   <si>
     <t>枯骨荒漠</t>
@@ -261,7 +327,7 @@
     <t>Player/Boss/Boss4</t>
   </si>
   <si>
-    <t>8,6</t>
+    <t>攻速</t>
   </si>
   <si>
     <t>迷雾森林</t>
@@ -270,7 +336,7 @@
     <t>Player/Boss/Boss5</t>
   </si>
   <si>
-    <t>9,7</t>
+    <t>命中</t>
   </si>
   <si>
     <t>熔火地穴</t>
@@ -279,7 +345,7 @@
     <t>Player/Boss/Boss6</t>
   </si>
   <si>
-    <t>10,8</t>
+    <t>闪避</t>
   </si>
   <si>
     <t>雷光废墟</t>
@@ -288,52 +354,34 @@
     <t>Player/Boss/Boss7</t>
   </si>
   <si>
-    <t>11,9</t>
-  </si>
-  <si>
     <t>冰封王陵</t>
   </si>
   <si>
     <t>Player/Boss/Boss8</t>
   </si>
   <si>
-    <t>12,10</t>
-  </si>
-  <si>
     <t>诅咒祭坛</t>
   </si>
   <si>
     <t>Player/Boss/Boss9</t>
   </si>
   <si>
-    <t>13,11</t>
-  </si>
-  <si>
     <t>虚空裂谷</t>
   </si>
   <si>
     <t>Player/Boss/Boss10</t>
   </si>
   <si>
-    <t>14,12</t>
-  </si>
-  <si>
     <t>龙眠之地</t>
   </si>
   <si>
     <t>Player/Boss/Boss11</t>
   </si>
   <si>
-    <t>15,13</t>
-  </si>
-  <si>
     <t>永恒神界</t>
   </si>
   <si>
     <t>Player/Boss/Boss12</t>
-  </si>
-  <si>
-    <t>16,14</t>
   </si>
 </sst>
 </file>
@@ -1311,32 +1359,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="15.5" style="1" customWidth="1"/>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="13.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5833333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="21.1666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.9166666666667" style="1" customWidth="1"/>
-    <col min="8" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.9166666666667" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="17.25" style="1" customWidth="1"/>
+    <col min="8" max="12" width="12.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.9166666666667" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:10">
+    <row r="1" customHeight="1" spans="3:13">
       <c r="F1" s="2"/>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:10">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:13">
       <c r="F2" s="2"/>
-      <c r="J2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1361,8 +1410,17 @@
       <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1387,34 +1445,52 @@
       <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>12</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1422,22 +1498,31 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>18</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1445,22 +1530,31 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="I7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1468,22 +1562,31 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:10">
+        <v>27</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:13">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1491,22 +1594,33 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:10">
+        <v>31</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" ref="J9:J14" si="0">J6+1</f>
+        <v>2</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" ref="L9:L41" si="1">L6+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:13">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1514,22 +1628,33 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:10">
+      <c r="J10" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:13">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1537,22 +1662,33 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:10">
+        <v>36</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K11" s="1">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:13">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1560,22 +1696,33 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:10">
+        <v>39</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:13">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1583,22 +1730,33 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:10">
+        <v>39</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:13">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1606,22 +1764,33 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:10">
+        <v>44</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="K14" s="1">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:13">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1629,22 +1798,33 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:10">
+        <v>46</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" ref="J15:J20" si="2">J12+1</f>
+        <v>4</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:13">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1652,22 +1832,33 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:9">
+        <v>46</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:12">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1675,196 +1866,237 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:9">
-      <c r="A18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="K17" s="1">
+        <v>10</v>
+      </c>
+      <c r="L17" s="1">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:12">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:12">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:12">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="K20" s="1">
+        <v>10</v>
+      </c>
+      <c r="L20" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:12">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="G21" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:9">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" ref="J21:J26" si="3">J18+1</f>
+        <v>6</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:12">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I22" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:9">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:12">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:9">
+        <v>59</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="K23" s="1">
+        <v>10</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:12">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -1878,22 +2110,33 @@
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I24" s="1">
+        <v>61</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:9">
+    <row r="25" customHeight="1" spans="1:12">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1907,22 +2150,33 @@
         <v>2</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I25" s="1">
+        <v>61</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:9">
+    <row r="26" customHeight="1" spans="1:12">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -1936,22 +2190,33 @@
         <v>2</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I26" s="1">
+        <v>64</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:9">
+      <c r="K26" s="1">
+        <v>10</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:12">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -1965,22 +2230,33 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I27" s="1">
+        <v>66</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" ref="J27:J32" si="4">J24+1</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:9">
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:12">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -1994,22 +2270,33 @@
         <v>2</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="1">
+        <v>66</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:9">
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:12">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -2023,22 +2310,33 @@
         <v>2</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I29" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:9">
+        <v>66</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="K29" s="1">
+        <v>10</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -2052,22 +2350,33 @@
         <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I30" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:9">
+        <v>70</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -2081,22 +2390,33 @@
         <v>3</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I31" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
+        <v>70</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:12">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -2110,22 +2430,33 @@
         <v>3</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I32" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:9">
+        <v>70</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="K32" s="1">
+        <v>10</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:12">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -2139,22 +2470,32 @@
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I33" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:9">
+        <v>74</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" ref="J33:J38" si="5">J30+1</f>
+        <v>10</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:12">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -2168,22 +2509,32 @@
         <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I34" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:9">
+        <v>74</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="1">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:12">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -2197,22 +2548,32 @@
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I35" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:9">
+        <v>74</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="K35" s="1">
+        <v>10</v>
+      </c>
+      <c r="L35" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:12">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -2226,22 +2587,32 @@
         <v>3</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I36" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:9">
+        <v>78</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:12">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -2255,22 +2626,32 @@
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I37" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:9">
+        <v>78</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:12">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -2284,22 +2665,32 @@
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I38" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:9">
+        <v>78</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="K38" s="1">
+        <v>10</v>
+      </c>
+      <c r="L38" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:12">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -2313,22 +2704,32 @@
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I39" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:9">
+        <v>82</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" ref="J39:J41" si="6">J36+1</f>
+        <v>12</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:12">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -2342,22 +2743,32 @@
         <v>3</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I40" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:9">
+        <v>82</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="K40" s="1">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:12">
       <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
@@ -2371,19 +2782,29 @@
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I41" s="1">
-        <v>8</v>
+        <v>82</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="K41" s="1">
+        <v>10</v>
+      </c>
+      <c r="L41" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2400,31 +2821,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="6" width="15.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.9166666666667" style="1" customWidth="1"/>
-    <col min="8" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.9166666666667" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="8" max="12" width="12.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="F1" s="2"/>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="F2" s="2"/>
-      <c r="J2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2449,8 +2869,17 @@
       <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2475,34 +2904,52 @@
       <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
+        <v>12</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C6" s="1">
         <v>1101</v>
       </c>
@@ -2510,22 +2957,34 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
+        <v>88</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J6" s="1">
+        <v>5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C7" s="1">
         <v>1102</v>
       </c>
@@ -2533,22 +2992,34 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" s="1">
+        <v>88</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C8" s="1">
         <v>1103</v>
       </c>
@@ -2556,22 +3027,34 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
+        <v>88</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J8" s="1">
+        <v>7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>4</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C9" s="1">
         <v>1104</v>
       </c>
@@ -2579,22 +3062,34 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
+        <v>88</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" s="1">
+        <v>8</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>5</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C10" s="1">
         <v>1105</v>
       </c>
@@ -2602,28 +3097,34 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I10" s="1">
+        <v>88</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J10" s="1">
+        <v>9</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="M10" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C11" s="1">
         <v>1106</v>
       </c>
@@ -2631,28 +3132,34 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I11" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J11" s="1">
+        <v>10</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>7</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C12" s="1">
         <v>1107</v>
       </c>
@@ -2660,22 +3167,31 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:10">
+        <v>88</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" s="1">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -2689,22 +3205,31 @@
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="H13" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I13" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J13" s="1">
+        <v>12</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -2718,22 +3243,31 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I14" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:10">
+        <v>88</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" s="1">
+        <v>13</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -2747,22 +3281,31 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="I15" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:10">
+        <v>88</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15" s="1">
+        <v>14</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -2776,22 +3319,31 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:9">
+        <v>88</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" s="1">
+        <v>15</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -2805,22 +3357,31 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:9">
+        <v>88</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J17" s="1">
+        <v>16</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:12">
       <c r="F18" s="2"/>
     </row>
   </sheetData>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -1519,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1551,7 +1551,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1583,7 +1583,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="L9" s="1">
         <f t="shared" ref="L9:L41" si="1">L6+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:13">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="L10" s="1">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:13">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="L11" s="1">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:13">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="L12" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:13">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="L13" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="L14" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:13">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L15" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:13">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="L16" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:12">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="L17" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="L18" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:12">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="L19" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:12">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="L20" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:12">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="L21" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:12">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="L22" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:12">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="L23" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:12">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="L24" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:12">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="L25" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:12">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="L26" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:12">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:12">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="L28" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:12">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="L29" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:12">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L30" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:12">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="L31" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:12">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="L32" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:12">

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -84,7 +84,7 @@
     <t>3,91</t>
   </si>
   <si>
-    <t>10,1</t>
+    <t>20,1</t>
   </si>
   <si>
     <t>1003</t>
@@ -123,7 +123,7 @@
     <t>Bag/Equip/Box_Equip_2_1</t>
   </si>
   <si>
-    <t>20,1</t>
+    <t>50,1</t>
   </si>
   <si>
     <t>10级衣服</t>
@@ -138,7 +138,7 @@
     <t>Bag/Equip/Box_Equip_2_3</t>
   </si>
   <si>
-    <t>400,1</t>
+    <t>500,1</t>
   </si>
   <si>
     <t>20级武器</t>
@@ -147,7 +147,7 @@
     <t>Bag/Equip/Box_Equip_3_1</t>
   </si>
   <si>
-    <t>30,1</t>
+    <t>90,1</t>
   </si>
   <si>
     <t>20级衣服</t>
@@ -162,13 +162,13 @@
     <t>Bag/Equip/Box_Equip_3_3</t>
   </si>
   <si>
-    <t>600,1</t>
+    <t>900,1</t>
   </si>
   <si>
     <t>30级武器</t>
   </si>
   <si>
-    <t>40,1</t>
+    <t>130,1</t>
   </si>
   <si>
     <t>30级衣服</t>
@@ -177,13 +177,13 @@
     <t>30级首饰</t>
   </si>
   <si>
-    <t>800,1</t>
+    <t>1300,1</t>
   </si>
   <si>
     <t>40级武器</t>
   </si>
   <si>
-    <t>50,1</t>
+    <t>180,1</t>
   </si>
   <si>
     <t>40级衣服</t>
@@ -192,13 +192,13 @@
     <t>40级首饰</t>
   </si>
   <si>
-    <t>1000,1</t>
+    <t>1800,1</t>
   </si>
   <si>
     <t>50级武器</t>
   </si>
   <si>
-    <t>60,1</t>
+    <t>240,1</t>
   </si>
   <si>
     <t>50级衣服</t>
@@ -207,7 +207,7 @@
     <t>50级首饰</t>
   </si>
   <si>
-    <t>1200,1</t>
+    <t>2400,1</t>
   </si>
   <si>
     <t>60级武器</t>
@@ -1580,7 +1580,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -1681,7 +1681,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" si="1"/>
@@ -1783,7 +1783,7 @@
         <v>4</v>
       </c>
       <c r="K14" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" si="1"/>
@@ -1885,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="K17" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" si="1"/>
@@ -1987,7 +1987,7 @@
         <v>6</v>
       </c>
       <c r="K20" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L20" s="1">
         <f t="shared" si="1"/>
@@ -2089,7 +2089,7 @@
         <v>7</v>
       </c>
       <c r="K23" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L23" s="1">
         <f t="shared" si="1"/>
@@ -2209,7 +2209,7 @@
         <v>8</v>
       </c>
       <c r="K26" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L26" s="1">
         <f t="shared" si="1"/>
@@ -2329,7 +2329,7 @@
         <v>9</v>
       </c>
       <c r="K29" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" si="1"/>
@@ -2449,7 +2449,7 @@
         <v>10</v>
       </c>
       <c r="K32" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L32" s="1">
         <f t="shared" si="1"/>
@@ -2567,7 +2567,7 @@
         <v>11</v>
       </c>
       <c r="K35" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L35" s="1">
         <v>10</v>
@@ -2684,7 +2684,7 @@
         <v>12</v>
       </c>
       <c r="K38" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L38" s="1">
         <v>10</v>
@@ -2801,7 +2801,7 @@
         <v>13</v>
       </c>
       <c r="K41" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L41" s="1">
         <v>10</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="117">
   <si>
     <t>#</t>
   </si>
@@ -84,7 +84,7 @@
     <t>3,91</t>
   </si>
   <si>
-    <t>20,1</t>
+    <t>50,1</t>
   </si>
   <si>
     <t>1003</t>
@@ -111,45 +111,45 @@
     <t>1,91</t>
   </si>
   <si>
+    <t>500,1</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>10级武器</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_2_1</t>
+  </si>
+  <si>
+    <t>100,1</t>
+  </si>
+  <si>
+    <t>10级衣服</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_2_2</t>
+  </si>
+  <si>
+    <t>10级首饰</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_2_3</t>
+  </si>
+  <si>
+    <t>1000,1</t>
+  </si>
+  <si>
+    <t>20级武器</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_3_1</t>
+  </si>
+  <si>
     <t>200,1</t>
   </si>
   <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>10级武器</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_2_1</t>
-  </si>
-  <si>
-    <t>50,1</t>
-  </si>
-  <si>
-    <t>10级衣服</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_2_2</t>
-  </si>
-  <si>
-    <t>10级首饰</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_2_3</t>
-  </si>
-  <si>
-    <t>500,1</t>
-  </si>
-  <si>
-    <t>20级武器</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_3_1</t>
-  </si>
-  <si>
-    <t>90,1</t>
-  </si>
-  <si>
     <t>20级衣服</t>
   </si>
   <si>
@@ -162,13 +162,13 @@
     <t>Bag/Equip/Box_Equip_3_3</t>
   </si>
   <si>
-    <t>900,1</t>
+    <t>2000,1</t>
   </si>
   <si>
     <t>30级武器</t>
   </si>
   <si>
-    <t>130,1</t>
+    <t>350,1</t>
   </si>
   <si>
     <t>30级衣服</t>
@@ -177,28 +177,25 @@
     <t>30级首饰</t>
   </si>
   <si>
-    <t>1300,1</t>
+    <t>3500,1</t>
   </si>
   <si>
     <t>40级武器</t>
   </si>
   <si>
-    <t>180,1</t>
-  </si>
-  <si>
     <t>40级衣服</t>
   </si>
   <si>
     <t>40级首饰</t>
   </si>
   <si>
-    <t>1800,1</t>
+    <t>5000,1</t>
   </si>
   <si>
     <t>50级武器</t>
   </si>
   <si>
-    <t>240,1</t>
+    <t>800,1</t>
   </si>
   <si>
     <t>50级衣服</t>
@@ -207,7 +204,7 @@
     <t>50级首饰</t>
   </si>
   <si>
-    <t>2400,1</t>
+    <t>8000,1</t>
   </si>
   <si>
     <t>60级武器</t>
@@ -1909,7 +1906,7 @@
         <v>17</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>19</v>
@@ -1934,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>33</v>
@@ -1943,7 +1940,7 @@
         <v>22</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>23</v>
@@ -1968,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>35</v>
@@ -1977,7 +1974,7 @@
         <v>26</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>28</v>
@@ -2002,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>38</v>
@@ -2011,7 +2008,7 @@
         <v>17</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>19</v>
@@ -2036,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>41</v>
@@ -2045,7 +2042,7 @@
         <v>22</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>23</v>
@@ -2070,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>43</v>
@@ -2079,7 +2076,7 @@
         <v>26</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>28</v>
@@ -2110,7 +2107,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>16</v>
@@ -2119,7 +2116,7 @@
         <v>17</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>19</v>
@@ -2150,7 +2147,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>21</v>
@@ -2159,7 +2156,7 @@
         <v>22</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>23</v>
@@ -2190,7 +2187,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>25</v>
@@ -2199,7 +2196,7 @@
         <v>26</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>28</v>
@@ -2230,7 +2227,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>30</v>
@@ -2239,7 +2236,7 @@
         <v>17</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>19</v>
@@ -2270,7 +2267,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>33</v>
@@ -2279,7 +2276,7 @@
         <v>22</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>23</v>
@@ -2310,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>35</v>
@@ -2319,7 +2316,7 @@
         <v>26</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>28</v>
@@ -2350,7 +2347,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>38</v>
@@ -2359,7 +2356,7 @@
         <v>17</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>19</v>
@@ -2390,7 +2387,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>41</v>
@@ -2399,7 +2396,7 @@
         <v>22</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>23</v>
@@ -2430,7 +2427,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>43</v>
@@ -2439,7 +2436,7 @@
         <v>26</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>28</v>
@@ -2470,7 +2467,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>16</v>
@@ -2479,7 +2476,7 @@
         <v>17</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>19</v>
@@ -2509,7 +2506,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>21</v>
@@ -2518,7 +2515,7 @@
         <v>22</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>23</v>
@@ -2548,7 +2545,7 @@
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>25</v>
@@ -2557,7 +2554,7 @@
         <v>26</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>28</v>
@@ -2587,7 +2584,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>30</v>
@@ -2596,7 +2593,7 @@
         <v>17</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>19</v>
@@ -2626,7 +2623,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>33</v>
@@ -2635,7 +2632,7 @@
         <v>22</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>23</v>
@@ -2665,7 +2662,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>35</v>
@@ -2674,7 +2671,7 @@
         <v>26</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>28</v>
@@ -2704,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>38</v>
@@ -2713,7 +2710,7 @@
         <v>17</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>19</v>
@@ -2743,7 +2740,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>41</v>
@@ -2752,7 +2749,7 @@
         <v>22</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>23</v>
@@ -2782,7 +2779,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>43</v>
@@ -2791,7 +2788,7 @@
         <v>26</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>28</v>
@@ -2957,19 +2954,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J6" s="1">
         <v>5</v>
@@ -2981,7 +2978,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -2992,19 +2989,19 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="G7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J7" s="1">
         <v>6</v>
@@ -3016,7 +3013,7 @@
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3027,19 +3024,19 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="G8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J8" s="1">
         <v>7</v>
@@ -3051,7 +3048,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3062,19 +3059,19 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="G9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J9" s="1">
         <v>8</v>
@@ -3086,7 +3083,7 @@
         <v>5</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3097,19 +3094,19 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="G10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J10" s="1">
         <v>9</v>
@@ -3121,7 +3118,7 @@
         <v>6</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3132,19 +3129,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="G11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J11" s="1">
         <v>10</v>
@@ -3156,7 +3153,7 @@
         <v>7</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3167,19 +3164,19 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="G12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J12" s="1">
         <v>11</v>
@@ -3205,19 +3202,19 @@
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="G13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J13" s="1">
         <v>12</v>
@@ -3243,19 +3240,19 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="G14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J14" s="1">
         <v>13</v>
@@ -3281,19 +3278,19 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="G15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J15" s="1">
         <v>14</v>
@@ -3319,19 +3316,19 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="G16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="I16" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J16" s="1">
         <v>15</v>
@@ -3357,19 +3354,19 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="G17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J17" s="1">
         <v>16</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -2975,7 +2975,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>89</v>
@@ -3010,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>92</v>
@@ -3045,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>95</v>
@@ -3080,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>98</v>
@@ -3115,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>101</v>
@@ -3150,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>104</v>
@@ -3185,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3223,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>1级武器</t>
+    <t>朽木武器</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_1_1</t>
@@ -90,7 +90,7 @@
     <t>1003</t>
   </si>
   <si>
-    <t>1级衣服</t>
+    <t>朽木衣服</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_1_2</t>
@@ -102,7 +102,7 @@
     <t>1002</t>
   </si>
   <si>
-    <t>1级首饰</t>
+    <t>朽木首饰</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_1_3</t>
@@ -117,7 +117,7 @@
     <t>1001</t>
   </si>
   <si>
-    <t>10级武器</t>
+    <t>黑铁武器</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_2_1</t>
@@ -126,13 +126,13 @@
     <t>100,1</t>
   </si>
   <si>
-    <t>10级衣服</t>
+    <t>黑铁衣服</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_2_2</t>
   </si>
   <si>
-    <t>10级首饰</t>
+    <t>黑铁首饰</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_2_3</t>
@@ -141,7 +141,7 @@
     <t>1000,1</t>
   </si>
   <si>
-    <t>20级武器</t>
+    <t>白银武器</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_3_1</t>
@@ -150,13 +150,13 @@
     <t>200,1</t>
   </si>
   <si>
-    <t>20级衣服</t>
+    <t>白银衣服</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_3_2</t>
   </si>
   <si>
-    <t>20级首饰</t>
+    <t>白银首饰</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_3_3</t>
@@ -165,121 +165,121 @@
     <t>2000,1</t>
   </si>
   <si>
-    <t>30级武器</t>
+    <t>黄金武器</t>
   </si>
   <si>
     <t>350,1</t>
   </si>
   <si>
-    <t>30级衣服</t>
-  </si>
-  <si>
-    <t>30级首饰</t>
+    <t>黄金衣服</t>
+  </si>
+  <si>
+    <t>黄金首饰</t>
   </si>
   <si>
     <t>3500,1</t>
   </si>
   <si>
-    <t>40级武器</t>
-  </si>
-  <si>
-    <t>40级衣服</t>
-  </si>
-  <si>
-    <t>40级首饰</t>
+    <t>钻石武器</t>
+  </si>
+  <si>
+    <t>钻石衣服</t>
+  </si>
+  <si>
+    <t>钻石首饰</t>
   </si>
   <si>
     <t>5000,1</t>
   </si>
   <si>
-    <t>50级武器</t>
+    <t>金龙武器</t>
   </si>
   <si>
     <t>800,1</t>
   </si>
   <si>
-    <t>50级衣服</t>
-  </si>
-  <si>
-    <t>50级首饰</t>
+    <t>金龙衣服</t>
+  </si>
+  <si>
+    <t>金龙首饰</t>
   </si>
   <si>
     <t>8000,1</t>
   </si>
   <si>
-    <t>60级武器</t>
+    <t>木龙武器</t>
   </si>
   <si>
     <t>70,1</t>
   </si>
   <si>
-    <t>60级衣服</t>
-  </si>
-  <si>
-    <t>60级首饰</t>
+    <t>木龙衣服</t>
+  </si>
+  <si>
+    <t>木龙首饰</t>
   </si>
   <si>
     <t>1400,1</t>
   </si>
   <si>
-    <t>70级武器</t>
+    <t>土龙武器</t>
   </si>
   <si>
     <t>8,4</t>
   </si>
   <si>
-    <t>70级衣服</t>
-  </si>
-  <si>
-    <t>70级首饰</t>
-  </si>
-  <si>
-    <t>80级武器</t>
+    <t>土龙衣服</t>
+  </si>
+  <si>
+    <t>土龙首饰</t>
+  </si>
+  <si>
+    <t>冰龙武器</t>
   </si>
   <si>
     <t>9,5</t>
   </si>
   <si>
-    <t>80级衣服</t>
-  </si>
-  <si>
-    <t>80级首饰</t>
-  </si>
-  <si>
-    <t>90级武器</t>
+    <t>冰龙衣服</t>
+  </si>
+  <si>
+    <t>冰龙首饰</t>
+  </si>
+  <si>
+    <t>炎龙武器</t>
   </si>
   <si>
     <t>10,5</t>
   </si>
   <si>
-    <t>90级衣服</t>
-  </si>
-  <si>
-    <t>90级首饰</t>
-  </si>
-  <si>
-    <t>100级武器</t>
+    <t>炎龙衣服</t>
+  </si>
+  <si>
+    <t>炎龙首饰</t>
+  </si>
+  <si>
+    <t>光龙武器</t>
   </si>
   <si>
     <t>11,6</t>
   </si>
   <si>
-    <t>100级衣服</t>
-  </si>
-  <si>
-    <t>100级首饰</t>
-  </si>
-  <si>
-    <t>110级武器</t>
+    <t>光龙衣服</t>
+  </si>
+  <si>
+    <t>光龙首饰</t>
+  </si>
+  <si>
+    <t>暗龙武器</t>
   </si>
   <si>
     <t>12,6</t>
   </si>
   <si>
-    <t>110级衣服</t>
-  </si>
-  <si>
-    <t>110级首饰</t>
+    <t>暗龙衣服</t>
+  </si>
+  <si>
+    <t>暗龙首饰</t>
   </si>
   <si>
     <t>落日平原</t>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="118">
   <si>
     <t>#</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>SpeAtrVue</t>
+  </si>
+  <si>
+    <t>SpeRequire</t>
   </si>
   <si>
     <t>BaseFee</t>
@@ -1356,7 +1359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1364,25 +1367,25 @@
     <col min="5" max="5" width="20.5833333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="21.1666666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="17.25" style="1" customWidth="1"/>
-    <col min="8" max="12" width="12.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.9166666666667" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="8" max="13" width="12.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="26.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.9166666666667" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:13">
+    <row r="1" customHeight="1" spans="3:14">
       <c r="F1" s="2"/>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:13">
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:14">
       <c r="F2" s="2"/>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1416,8 +1419,11 @@
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1451,43 +1457,49 @@
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1495,31 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1527,31 +1542,34 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L7" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1559,19 +1577,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J8" s="1">
         <v>2</v>
@@ -1580,10 +1598,13 @@
         <v>5</v>
       </c>
       <c r="L8" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:13">
+        <v>5</v>
+      </c>
+      <c r="M8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1591,33 +1612,37 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" ref="J9:J14" si="0">J6+1</f>
         <v>2</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <f t="shared" ref="K9:K32" si="1">K6+1</f>
+        <v>6</v>
       </c>
       <c r="L9" s="1">
-        <f t="shared" ref="L9:L41" si="1">L6+1</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
+        <f t="shared" ref="M9:M23" si="2">M6+1</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:14">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1625,33 +1650,37 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="I10" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="K10" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:14">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1659,33 +1688,37 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="K11" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L11" s="1">
         <v>5</v>
       </c>
-      <c r="L11" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:13">
+      <c r="M11" s="1">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:14">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1693,33 +1726,37 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="K12" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:14">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1727,33 +1764,37 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="I13" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:14">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1761,67 +1802,75 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="K14" s="1">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="L14" s="1">
         <v>5</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:14">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" ref="J15:J20" si="3">J12+1</f>
+        <v>4</v>
+      </c>
+      <c r="K15" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="1">
-        <f t="shared" ref="J15:J20" si="2">J12+1</f>
-        <v>4</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:14">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1829,33 +1878,37 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="I16" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="K16" s="1">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:13">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1863,33 +1916,37 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J17" s="1">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="K17" s="1">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="K17" s="1">
-        <v>5</v>
-      </c>
-      <c r="L17" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:13">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1897,33 +1954,37 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="1">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:13">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1931,33 +1992,37 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J19" s="1">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="K19" s="1">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="K19" s="1">
-        <v>1</v>
-      </c>
-      <c r="L19" s="1">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:13">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1965,33 +2030,37 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" s="1">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="K20" s="1">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="M20" s="1">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="K20" s="1">
-        <v>5</v>
-      </c>
-      <c r="L20" s="1">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:13">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1999,33 +2068,37 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" ref="J21:J26" si="3">J18+1</f>
+        <f t="shared" ref="J21:J26" si="4">J18+1</f>
         <v>6</v>
       </c>
       <c r="K21" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:13">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2033,33 +2106,37 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="I22" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="K22" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="L22" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:13">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -2067,33 +2144,37 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="K23" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L23" s="1">
         <v>5</v>
       </c>
-      <c r="L23" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:12">
+      <c r="M23" s="1">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:13">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -2107,33 +2188,35 @@
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="K24" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L24" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:13">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -2147,33 +2230,35 @@
         <v>2</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>60</v>
-      </c>
       <c r="I25" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="K25" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:13">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -2187,33 +2272,35 @@
         <v>2</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="K26" s="1">
+        <v>10</v>
+      </c>
+      <c r="L26" s="1">
         <v>5</v>
       </c>
-      <c r="L26" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:12">
+      <c r="M26" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:13">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -2227,33 +2314,35 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" ref="J27:J32" si="4">J24+1</f>
+        <f t="shared" ref="J27:J32" si="5">J24+1</f>
         <v>8</v>
       </c>
       <c r="K27" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L27" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:13">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -2267,33 +2356,35 @@
         <v>2</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>65</v>
-      </c>
       <c r="I28" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="K28" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L28" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:13">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -2307,33 +2398,35 @@
         <v>2</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="K29" s="1">
+        <v>10</v>
+      </c>
+      <c r="L29" s="1">
         <v>5</v>
       </c>
-      <c r="L29" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:12">
+      <c r="M29" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:13">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -2347,33 +2440,35 @@
         <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="K30" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L30" s="1">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:13">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -2387,33 +2482,35 @@
         <v>3</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="I31" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="K31" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:13">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -2427,33 +2524,35 @@
         <v>3</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="K32" s="1">
+        <v>10</v>
+      </c>
+      <c r="L32" s="1">
         <v>5</v>
       </c>
-      <c r="L32" s="1">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:12">
+      <c r="M32" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:13">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -2467,32 +2566,35 @@
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" ref="J33:J38" si="5">J30+1</f>
+        <f t="shared" ref="J33:J38" si="6">J30+1</f>
         <v>10</v>
       </c>
       <c r="K33" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L33" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:13">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -2506,32 +2608,35 @@
         <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="I34" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="K34" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L34" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:13">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -2545,32 +2650,35 @@
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="K35" s="1">
+        <v>10</v>
+      </c>
+      <c r="L35" s="1">
         <v>5</v>
       </c>
-      <c r="L35" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:12">
+      <c r="M35" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:13">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -2584,32 +2692,35 @@
         <v>3</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="K36" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L36" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:13">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -2623,32 +2734,35 @@
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="I37" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="K37" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L37" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:13">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -2662,32 +2776,35 @@
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="K38" s="1">
+        <v>10</v>
+      </c>
+      <c r="L38" s="1">
         <v>5</v>
       </c>
-      <c r="L38" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:12">
+      <c r="M38" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:13">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -2701,32 +2818,35 @@
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" ref="J39:J41" si="6">J36+1</f>
+        <f t="shared" ref="J39:J41" si="7">J36+1</f>
         <v>12</v>
       </c>
       <c r="K39" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L39" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:13">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -2740,32 +2860,35 @@
         <v>3</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="I40" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="K40" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L40" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:13">
       <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
@@ -2779,28 +2902,31 @@
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="K41" s="1">
+        <v>10</v>
+      </c>
+      <c r="L41" s="1">
         <v>5</v>
       </c>
-      <c r="L41" s="1">
+      <c r="M41" s="1">
         <v>10</v>
       </c>
     </row>
@@ -2818,30 +2944,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="6" width="15.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.9166666666667" style="1" customWidth="1"/>
-    <col min="8" max="12" width="12.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="8" max="13" width="12.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="26.75" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="F1" s="2"/>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="F2" s="2"/>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2875,8 +3001,11 @@
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2910,43 +3039,49 @@
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C6" s="1">
         <v>1101</v>
       </c>
@@ -2954,34 +3089,37 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J6" s="1">
         <v>5</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6" s="1">
-        <v>3</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>5</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C7" s="1">
         <v>1102</v>
       </c>
@@ -2989,34 +3127,37 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J7" s="1">
         <v>6</v>
       </c>
       <c r="K7" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L7" s="1">
-        <v>4</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>6</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C8" s="1">
         <v>1103</v>
       </c>
@@ -3024,34 +3165,37 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J8" s="1">
         <v>7</v>
       </c>
       <c r="K8" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L8" s="1">
-        <v>5</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>7</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C9" s="1">
         <v>1104</v>
       </c>
@@ -3059,34 +3203,37 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J9" s="1">
         <v>8</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L9" s="1">
-        <v>6</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
+        <v>8</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C10" s="1">
         <v>1105</v>
       </c>
@@ -3094,34 +3241,37 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" s="1">
         <v>9</v>
       </c>
       <c r="K10" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1">
-        <v>7</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
+        <v>9</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C11" s="1">
         <v>1106</v>
       </c>
@@ -3129,34 +3279,37 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J11" s="1">
         <v>10</v>
       </c>
       <c r="K11" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L11" s="1">
-        <v>8</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C12" s="1">
         <v>1107</v>
       </c>
@@ -3164,31 +3317,34 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J12" s="1">
         <v>11</v>
       </c>
       <c r="K12" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L12" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -3202,31 +3358,34 @@
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J13" s="1">
         <v>12</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L13" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -3240,31 +3399,34 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J14" s="1">
         <v>13</v>
       </c>
       <c r="K14" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L14" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -3278,31 +3440,34 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J15" s="1">
         <v>14</v>
       </c>
       <c r="K15" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L15" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -3316,31 +3481,34 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J16" s="1">
         <v>15</v>
       </c>
       <c r="K16" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L16" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -3354,31 +3522,34 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" s="1">
         <v>16</v>
       </c>
       <c r="K17" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:13">
       <c r="F18" s="2"/>
     </row>
   </sheetData>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="136">
   <si>
     <t>#</t>
   </si>
@@ -87,7 +87,7 @@
     <t>3,91</t>
   </si>
   <si>
-    <t>50,1</t>
+    <t>100,1</t>
   </si>
   <si>
     <t>1003</t>
@@ -114,7 +114,7 @@
     <t>1,91</t>
   </si>
   <si>
-    <t>500,1</t>
+    <t>1000,1</t>
   </si>
   <si>
     <t>1001</t>
@@ -126,7 +126,7 @@
     <t>Bag/Equip/Box_Equip_2_1</t>
   </si>
   <si>
-    <t>100,1</t>
+    <t>200,1</t>
   </si>
   <si>
     <t>黑铁衣服</t>
@@ -141,7 +141,7 @@
     <t>Bag/Equip/Box_Equip_2_3</t>
   </si>
   <si>
-    <t>1000,1</t>
+    <t>2000,1</t>
   </si>
   <si>
     <t>白银武器</t>
@@ -150,7 +150,7 @@
     <t>Bag/Equip/Box_Equip_3_1</t>
   </si>
   <si>
-    <t>200,1</t>
+    <t>300,1</t>
   </si>
   <si>
     <t>白银衣服</t>
@@ -165,13 +165,13 @@
     <t>Bag/Equip/Box_Equip_3_3</t>
   </si>
   <si>
-    <t>2000,1</t>
+    <t>3000,1</t>
   </si>
   <si>
     <t>黄金武器</t>
   </si>
   <si>
-    <t>350,1</t>
+    <t>400,1</t>
   </si>
   <si>
     <t>黄金衣服</t>
@@ -180,19 +180,22 @@
     <t>黄金首饰</t>
   </si>
   <si>
-    <t>3500,1</t>
+    <t>4000,1</t>
   </si>
   <si>
     <t>钻石武器</t>
   </si>
   <si>
+    <t>600,1</t>
+  </si>
+  <si>
     <t>钻石衣服</t>
   </si>
   <si>
     <t>钻石首饰</t>
   </si>
   <si>
-    <t>5000,1</t>
+    <t>6000,1</t>
   </si>
   <si>
     <t>金龙武器</t>
@@ -297,7 +300,7 @@
     <t>1,1</t>
   </si>
   <si>
-    <t>27</t>
+    <t>21</t>
   </si>
   <si>
     <t>暴击</t>
@@ -309,6 +312,9 @@
     <t>Player/Boss/Boss2</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>爆伤</t>
   </si>
   <si>
@@ -318,6 +324,9 @@
     <t>Player/Boss/Boss3</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>冷却</t>
   </si>
   <si>
@@ -327,6 +336,9 @@
     <t>Player/Boss/Boss4</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>攻速</t>
   </si>
   <si>
@@ -336,6 +348,9 @@
     <t>Player/Boss/Boss5</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>命中</t>
   </si>
   <si>
@@ -345,6 +360,9 @@
     <t>Player/Boss/Boss6</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>闪避</t>
   </si>
   <si>
@@ -354,34 +372,70 @@
     <t>Player/Boss/Boss7</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
     <t>冰封王陵</t>
   </si>
   <si>
     <t>Player/Boss/Boss8</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>幸运</t>
+  </si>
+  <si>
     <t>诅咒祭坛</t>
   </si>
   <si>
     <t>Player/Boss/Boss9</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>诅咒</t>
+  </si>
+  <si>
     <t>虚空裂谷</t>
   </si>
   <si>
     <t>Player/Boss/Boss10</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>生命增幅</t>
+  </si>
+  <si>
     <t>龙眠之地</t>
   </si>
   <si>
     <t>Player/Boss/Boss11</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>防御增幅</t>
+  </si>
+  <si>
     <t>永恒神界</t>
   </si>
   <si>
     <t>Player/Boss/Boss12</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>攻击增幅</t>
   </si>
 </sst>
 </file>
@@ -1963,7 +2017,7 @@
         <v>18</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>20</v>
@@ -1992,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>34</v>
@@ -2001,7 +2055,7 @@
         <v>23</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>24</v>
@@ -2030,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>36</v>
@@ -2039,7 +2093,7 @@
         <v>27</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>29</v>
@@ -2068,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>39</v>
@@ -2077,7 +2131,7 @@
         <v>18</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>20</v>
@@ -2106,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>42</v>
@@ -2115,7 +2169,7 @@
         <v>23</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>24</v>
@@ -2144,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>44</v>
@@ -2153,7 +2207,7 @@
         <v>27</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>29</v>
@@ -2188,7 +2242,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>17</v>
@@ -2197,7 +2251,7 @@
         <v>18</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>20</v>
@@ -2230,7 +2284,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>22</v>
@@ -2239,7 +2293,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>24</v>
@@ -2272,7 +2326,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>26</v>
@@ -2281,7 +2335,7 @@
         <v>27</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>29</v>
@@ -2314,7 +2368,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>31</v>
@@ -2323,7 +2377,7 @@
         <v>18</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>20</v>
@@ -2356,7 +2410,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>34</v>
@@ -2365,7 +2419,7 @@
         <v>23</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>24</v>
@@ -2398,7 +2452,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>36</v>
@@ -2407,7 +2461,7 @@
         <v>27</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>29</v>
@@ -2440,7 +2494,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>39</v>
@@ -2449,7 +2503,7 @@
         <v>18</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>20</v>
@@ -2482,7 +2536,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>42</v>
@@ -2491,7 +2545,7 @@
         <v>23</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>24</v>
@@ -2524,7 +2578,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>44</v>
@@ -2533,7 +2587,7 @@
         <v>27</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>29</v>
@@ -2566,7 +2620,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>17</v>
@@ -2575,7 +2629,7 @@
         <v>18</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>20</v>
@@ -2608,7 +2662,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>22</v>
@@ -2617,7 +2671,7 @@
         <v>23</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>24</v>
@@ -2650,7 +2704,7 @@
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>26</v>
@@ -2659,7 +2713,7 @@
         <v>27</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>29</v>
@@ -2692,7 +2746,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>31</v>
@@ -2701,7 +2755,7 @@
         <v>18</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>20</v>
@@ -2734,7 +2788,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>34</v>
@@ -2743,7 +2797,7 @@
         <v>23</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>24</v>
@@ -2776,7 +2830,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>36</v>
@@ -2785,7 +2839,7 @@
         <v>27</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>29</v>
@@ -2818,7 +2872,7 @@
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>39</v>
@@ -2827,7 +2881,7 @@
         <v>18</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>20</v>
@@ -2860,7 +2914,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>42</v>
@@ -2869,7 +2923,7 @@
         <v>23</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>24</v>
@@ -2902,7 +2956,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>44</v>
@@ -2911,7 +2965,7 @@
         <v>27</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>29</v>
@@ -3089,19 +3143,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J6" s="1">
         <v>5</v>
@@ -3116,7 +3170,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3127,25 +3181,25 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J7" s="1">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K7" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L7" s="1">
         <v>1</v>
@@ -3154,7 +3208,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3165,22 +3219,22 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="J8" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1">
         <v>7</v>
@@ -3192,7 +3246,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3203,25 +3257,25 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="J9" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K9" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L9" s="1">
         <v>1</v>
@@ -3230,7 +3284,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3241,22 +3295,22 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="J10" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10" s="1">
         <v>9</v>
@@ -3268,7 +3322,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3279,25 +3333,25 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="J11" s="1">
         <v>10</v>
       </c>
       <c r="K11" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1">
         <v>1</v>
@@ -3306,7 +3360,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3317,22 +3371,22 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="J12" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K12" s="1">
         <v>10</v>
@@ -3342,6 +3396,9 @@
       </c>
       <c r="M12" s="1">
         <v>10</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3358,22 +3415,22 @@
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="J13" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
         <v>10</v>
@@ -3383,6 +3440,9 @@
       </c>
       <c r="M13" s="1">
         <v>10</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3399,22 +3459,22 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="J14" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
         <v>10</v>
@@ -3424,6 +3484,9 @@
       </c>
       <c r="M14" s="1">
         <v>10</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3440,22 +3503,22 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="J15" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" s="1">
         <v>10</v>
@@ -3465,6 +3528,9 @@
       </c>
       <c r="M15" s="1">
         <v>10</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3481,19 +3547,19 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="J16" s="1">
         <v>15</v>
@@ -3507,8 +3573,11 @@
       <c r="M16" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N16" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -3522,22 +3591,22 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="J17" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K17" s="1">
         <v>10</v>
@@ -3548,8 +3617,11 @@
       <c r="M17" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:13">
+      <c r="N17" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:14">
       <c r="F18" s="2"/>
     </row>
   </sheetData>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -1576,7 +1576,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         <v>24</v>
       </c>
       <c r="J7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
@@ -1646,7 +1646,7 @@
         <v>29</v>
       </c>
       <c r="J8" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1">
         <v>5</v>
@@ -1681,18 +1681,17 @@
         <v>20</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" ref="J9:J14" si="0">J6+1</f>
-        <v>2</v>
+        <f t="shared" ref="J9:J13" si="0">J6+1</f>
+        <v>3</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" ref="K9:K32" si="1">K6+1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9" s="1">
         <v>1</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" ref="M9:M23" si="2">M6+1</f>
+        <f t="shared" ref="M9:M23" si="1">M6+1</f>
         <v>6</v>
       </c>
     </row>
@@ -1720,17 +1719,16 @@
       </c>
       <c r="J10" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="1">
+        <v>5</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1">
-        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
@@ -1757,18 +1755,17 @@
         <v>29</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>J8+2</f>
+        <v>6</v>
       </c>
       <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>5</v>
+      </c>
+      <c r="M11" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L11" s="1">
-        <v>5</v>
-      </c>
-      <c r="M11" s="1">
-        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
@@ -1796,17 +1793,16 @@
       </c>
       <c r="J12" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
+        <v>5</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="L12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1834,17 +1830,16 @@
       </c>
       <c r="J13" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="1">
+        <v>5</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1871,20 +1866,19 @@
         <v>29</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>J11+2</f>
+        <v>8</v>
       </c>
       <c r="K14" s="1">
+        <v>5</v>
+      </c>
+      <c r="L14" s="1">
+        <v>5</v>
+      </c>
+      <c r="M14" s="1">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="L14" s="1">
-        <v>5</v>
-      </c>
-      <c r="M14" s="1">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
     </row>
     <row r="15" customHeight="1" spans="3:14">
       <c r="C15" s="1">
@@ -1909,18 +1903,17 @@
         <v>20</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" ref="J15:J20" si="3">J12+1</f>
-        <v>4</v>
+        <f t="shared" ref="J15:J19" si="2">J12+1</f>
+        <v>5</v>
       </c>
       <c r="K15" s="1">
+        <v>5</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L15" s="1">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -1947,18 +1940,17 @@
         <v>24</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="K16" s="1">
+        <v>5</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L16" s="1">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -1985,18 +1977,17 @@
         <v>29</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f>J14+2</f>
+        <v>10</v>
       </c>
       <c r="K17" s="1">
+        <v>5</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L17" s="1">
-        <v>5</v>
-      </c>
-      <c r="M17" s="1">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -2023,18 +2014,17 @@
         <v>20</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="K18" s="1">
+        <v>5</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L18" s="1">
-        <v>1</v>
-      </c>
-      <c r="M18" s="1">
-        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
@@ -2061,18 +2051,17 @@
         <v>24</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="K19" s="1">
+        <v>5</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L19" s="1">
-        <v>1</v>
-      </c>
-      <c r="M19" s="1">
-        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
@@ -2099,18 +2088,17 @@
         <v>29</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="3"/>
-        <v>6</v>
+        <f>J17+2</f>
+        <v>12</v>
       </c>
       <c r="K20" s="1">
+        <v>5</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="M20" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L20" s="1">
-        <v>5</v>
-      </c>
-      <c r="M20" s="1">
-        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
@@ -2137,18 +2125,17 @@
         <v>20</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" ref="J21:J26" si="4">J18+1</f>
-        <v>6</v>
+        <f t="shared" ref="J21:J25" si="3">J18+1</f>
+        <v>7</v>
       </c>
       <c r="K21" s="1">
+        <v>5</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L21" s="1">
-        <v>1</v>
-      </c>
-      <c r="M21" s="1">
-        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -2175,18 +2162,17 @@
         <v>24</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="4"/>
-        <v>6</v>
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="K22" s="1">
+        <v>5</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L22" s="1">
-        <v>1</v>
-      </c>
-      <c r="M22" s="1">
-        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -2213,18 +2199,17 @@
         <v>29</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="4"/>
-        <v>7</v>
+        <f>J20+2</f>
+        <v>14</v>
       </c>
       <c r="K23" s="1">
+        <v>5</v>
+      </c>
+      <c r="L23" s="1">
+        <v>5</v>
+      </c>
+      <c r="M23" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L23" s="1">
-        <v>5</v>
-      </c>
-      <c r="M23" s="1">
-        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -2257,8 +2242,8 @@
         <v>20</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="4"/>
-        <v>7</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="K24" s="1">
         <v>10</v>
@@ -2299,8 +2284,8 @@
         <v>24</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="4"/>
-        <v>7</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="K25" s="1">
         <v>10</v>
@@ -2341,8 +2326,8 @@
         <v>29</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="4"/>
-        <v>8</v>
+        <f>J23+2</f>
+        <v>16</v>
       </c>
       <c r="K26" s="1">
         <v>10</v>
@@ -2383,8 +2368,8 @@
         <v>20</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" ref="J27:J32" si="5">J24+1</f>
-        <v>8</v>
+        <f t="shared" ref="J27:J31" si="4">J24+1</f>
+        <v>9</v>
       </c>
       <c r="K27" s="1">
         <v>10</v>
@@ -2425,8 +2410,8 @@
         <v>24</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="5"/>
-        <v>8</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="K28" s="1">
         <v>10</v>
@@ -2467,8 +2452,8 @@
         <v>29</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="5"/>
-        <v>9</v>
+        <f>J26+2</f>
+        <v>18</v>
       </c>
       <c r="K29" s="1">
         <v>10</v>
@@ -2509,8 +2494,8 @@
         <v>20</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="5"/>
-        <v>9</v>
+        <f t="shared" si="4"/>
+        <v>10</v>
       </c>
       <c r="K30" s="1">
         <v>10</v>
@@ -2551,8 +2536,8 @@
         <v>24</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="5"/>
-        <v>9</v>
+        <f t="shared" si="4"/>
+        <v>10</v>
       </c>
       <c r="K31" s="1">
         <v>10</v>
@@ -2593,8 +2578,8 @@
         <v>29</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>J29+2</f>
+        <v>20</v>
       </c>
       <c r="K32" s="1">
         <v>10</v>
@@ -2635,8 +2620,8 @@
         <v>20</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" ref="J33:J38" si="6">J30+1</f>
-        <v>10</v>
+        <f t="shared" ref="J33:J37" si="5">J30+1</f>
+        <v>11</v>
       </c>
       <c r="K33" s="1">
         <v>10</v>
@@ -2677,8 +2662,8 @@
         <v>24</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="6"/>
-        <v>10</v>
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="K34" s="1">
         <v>10</v>
@@ -2719,8 +2704,8 @@
         <v>29</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="6"/>
-        <v>11</v>
+        <f>J32+2</f>
+        <v>22</v>
       </c>
       <c r="K35" s="1">
         <v>10</v>
@@ -2761,8 +2746,8 @@
         <v>20</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="6"/>
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="K36" s="1">
         <v>10</v>
@@ -2803,8 +2788,8 @@
         <v>24</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="6"/>
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="K37" s="1">
         <v>10</v>
@@ -2845,8 +2830,8 @@
         <v>29</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="6"/>
-        <v>12</v>
+        <f>J35+2</f>
+        <v>24</v>
       </c>
       <c r="K38" s="1">
         <v>10</v>
@@ -2887,8 +2872,8 @@
         <v>20</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" ref="J39:J41" si="7">J36+1</f>
-        <v>12</v>
+        <f>J36+1</f>
+        <v>13</v>
       </c>
       <c r="K39" s="1">
         <v>10</v>
@@ -2929,8 +2914,8 @@
         <v>24</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="7"/>
-        <v>12</v>
+        <f>J37+1</f>
+        <v>13</v>
       </c>
       <c r="K40" s="1">
         <v>10</v>
@@ -2971,8 +2956,8 @@
         <v>29</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="7"/>
-        <v>13</v>
+        <f>J38+2</f>
+        <v>26</v>
       </c>
       <c r="K41" s="1">
         <v>10</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -1685,13 +1685,12 @@
         <v>3</v>
       </c>
       <c r="K9" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9" s="1">
         <v>1</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" ref="M9:M23" si="1">M6+1</f>
         <v>6</v>
       </c>
     </row>
@@ -1722,13 +1721,12 @@
         <v>3</v>
       </c>
       <c r="K10" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10" s="1">
         <v>1</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
@@ -1759,13 +1757,12 @@
         <v>6</v>
       </c>
       <c r="K11" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11" s="1">
         <v>5</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
@@ -1796,13 +1793,12 @@
         <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L12" s="1">
         <v>1</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -1833,13 +1829,12 @@
         <v>4</v>
       </c>
       <c r="K13" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -1870,13 +1865,12 @@
         <v>8</v>
       </c>
       <c r="K14" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -1903,17 +1897,16 @@
         <v>20</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" ref="J15:J19" si="2">J12+1</f>
+        <f t="shared" ref="J15:J19" si="1">J12+1</f>
         <v>5</v>
       </c>
       <c r="K15" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L15" s="1">
         <v>1</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -1940,17 +1933,16 @@
         <v>24</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="K16" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L16" s="1">
         <v>1</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -1981,13 +1973,12 @@
         <v>10</v>
       </c>
       <c r="K17" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -2014,17 +2005,16 @@
         <v>20</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K18" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L18" s="1">
         <v>1</v>
       </c>
       <c r="M18" s="1">
-        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -2051,17 +2041,16 @@
         <v>24</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K19" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L19" s="1">
         <v>1</v>
       </c>
       <c r="M19" s="1">
-        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -2092,13 +2081,12 @@
         <v>12</v>
       </c>
       <c r="K20" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1">
-        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -2125,17 +2113,16 @@
         <v>20</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" ref="J21:J25" si="3">J18+1</f>
+        <f t="shared" ref="J21:J25" si="2">J18+1</f>
         <v>7</v>
       </c>
       <c r="K21" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L21" s="1">
         <v>1</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -2162,17 +2149,16 @@
         <v>24</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="K22" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L22" s="1">
         <v>1</v>
       </c>
       <c r="M22" s="1">
-        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -2203,13 +2189,12 @@
         <v>14</v>
       </c>
       <c r="K23" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="1">
-        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -2242,7 +2227,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="K24" s="1">
@@ -2284,7 +2269,7 @@
         <v>24</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="K25" s="1">
@@ -2368,7 +2353,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" ref="J27:J31" si="4">J24+1</f>
+        <f t="shared" ref="J27:J31" si="3">J24+1</f>
         <v>9</v>
       </c>
       <c r="K27" s="1">
@@ -2410,7 +2395,7 @@
         <v>24</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="K28" s="1">
@@ -2494,7 +2479,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="K30" s="1">
@@ -2536,7 +2521,7 @@
         <v>24</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="K31" s="1">
@@ -2620,7 +2605,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" ref="J33:J37" si="5">J30+1</f>
+        <f t="shared" ref="J33:J37" si="4">J30+1</f>
         <v>11</v>
       </c>
       <c r="K33" s="1">
@@ -2662,7 +2647,7 @@
         <v>24</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="K34" s="1">
@@ -2746,7 +2731,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="K36" s="1">
@@ -2788,7 +2773,7 @@
         <v>24</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="K37" s="1">
@@ -3184,7 +3169,7 @@
         <v>20</v>
       </c>
       <c r="K7" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7" s="1">
         <v>1</v>
@@ -3260,7 +3245,7 @@
         <v>5</v>
       </c>
       <c r="K9" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L9" s="1">
         <v>1</v>
@@ -3336,7 +3321,7 @@
         <v>10</v>
       </c>
       <c r="K11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" s="1">
         <v>1</v>
@@ -3374,13 +3359,13 @@
         <v>10</v>
       </c>
       <c r="K12" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L12" s="1">
         <v>1</v>
       </c>
       <c r="M12" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>115</v>
@@ -3418,13 +3403,13 @@
         <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
       </c>
       <c r="M13" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>119</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -3359,7 +3359,7 @@
         <v>10</v>
       </c>
       <c r="K12" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L12" s="1">
         <v>1</v>
@@ -3403,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
@@ -3453,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>123</v>
@@ -3497,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>127</v>
@@ -3541,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>131</v>
@@ -3585,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>135</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -3128,7 +3128,7 @@
         <v>90</v>
       </c>
       <c r="J6" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1">
         <v>5</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="140">
   <si>
     <t>#</t>
   </si>
@@ -186,64 +191,67 @@
     <t>钻石武器</t>
   </si>
   <si>
+    <t>500,1</t>
+  </si>
+  <si>
+    <t>钻石衣服</t>
+  </si>
+  <si>
+    <t>钻石首饰</t>
+  </si>
+  <si>
+    <t>5000,1</t>
+  </si>
+  <si>
+    <t>金龙武器</t>
+  </si>
+  <si>
     <t>600,1</t>
   </si>
   <si>
-    <t>钻石衣服</t>
-  </si>
-  <si>
-    <t>钻石首饰</t>
+    <t>金龙衣服</t>
+  </si>
+  <si>
+    <t>金龙首饰</t>
   </si>
   <si>
     <t>6000,1</t>
   </si>
   <si>
-    <t>金龙武器</t>
+    <t>木龙武器</t>
+  </si>
+  <si>
+    <t>700,1</t>
+  </si>
+  <si>
+    <t>木龙衣服</t>
+  </si>
+  <si>
+    <t>木龙首饰</t>
+  </si>
+  <si>
+    <t>7000,1</t>
+  </si>
+  <si>
+    <t>土龙武器</t>
   </si>
   <si>
     <t>800,1</t>
   </si>
   <si>
-    <t>金龙衣服</t>
-  </si>
-  <si>
-    <t>金龙首饰</t>
+    <t>土龙衣服</t>
+  </si>
+  <si>
+    <t>土龙首饰</t>
   </si>
   <si>
     <t>8000,1</t>
   </si>
   <si>
-    <t>木龙武器</t>
-  </si>
-  <si>
-    <t>70,1</t>
-  </si>
-  <si>
-    <t>木龙衣服</t>
-  </si>
-  <si>
-    <t>木龙首饰</t>
-  </si>
-  <si>
-    <t>1400,1</t>
-  </si>
-  <si>
-    <t>土龙武器</t>
-  </si>
-  <si>
-    <t>8,4</t>
-  </si>
-  <si>
-    <t>土龙衣服</t>
-  </si>
-  <si>
-    <t>土龙首饰</t>
-  </si>
-  <si>
     <t>冰龙武器</t>
   </si>
   <si>
-    <t>9,5</t>
+    <t>900,1</t>
   </si>
   <si>
     <t>冰龙衣服</t>
@@ -252,22 +260,25 @@
     <t>冰龙首饰</t>
   </si>
   <si>
+    <t>9000,1</t>
+  </si>
+  <si>
     <t>炎龙武器</t>
   </si>
   <si>
-    <t>10,5</t>
-  </si>
-  <si>
     <t>炎龙衣服</t>
   </si>
   <si>
     <t>炎龙首饰</t>
   </si>
   <si>
+    <t>10000,1</t>
+  </si>
+  <si>
     <t>光龙武器</t>
   </si>
   <si>
-    <t>11,6</t>
+    <t>1100,1</t>
   </si>
   <si>
     <t>光龙衣服</t>
@@ -276,16 +287,22 @@
     <t>光龙首饰</t>
   </si>
   <si>
+    <t>11000,1</t>
+  </si>
+  <si>
     <t>暗龙武器</t>
   </si>
   <si>
-    <t>12,6</t>
+    <t>1200,1</t>
   </si>
   <si>
     <t>暗龙衣服</t>
   </si>
   <si>
     <t>暗龙首饰</t>
+  </si>
+  <si>
+    <t>12000,1</t>
   </si>
   <si>
     <t>落日平原</t>
@@ -2431,7 +2448,7 @@
         <v>27</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>29</v>
@@ -2464,7 +2481,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>39</v>
@@ -2473,7 +2490,7 @@
         <v>18</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>20</v>
@@ -2506,7 +2523,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>42</v>
@@ -2515,7 +2532,7 @@
         <v>23</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>24</v>
@@ -2548,7 +2565,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>44</v>
@@ -2557,7 +2574,7 @@
         <v>27</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>29</v>
@@ -2590,7 +2607,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>17</v>
@@ -2599,7 +2616,7 @@
         <v>18</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>20</v>
@@ -2632,7 +2649,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>22</v>
@@ -2641,7 +2658,7 @@
         <v>23</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>24</v>
@@ -2674,7 +2691,7 @@
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>26</v>
@@ -2683,7 +2700,7 @@
         <v>27</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>29</v>
@@ -2716,7 +2733,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>31</v>
@@ -2725,7 +2742,7 @@
         <v>18</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>20</v>
@@ -2758,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>34</v>
@@ -2767,7 +2784,7 @@
         <v>23</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>24</v>
@@ -2800,7 +2817,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>36</v>
@@ -2809,7 +2826,7 @@
         <v>27</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>29</v>
@@ -2842,7 +2859,7 @@
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>39</v>
@@ -2851,7 +2868,7 @@
         <v>18</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>20</v>
@@ -2884,7 +2901,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>42</v>
@@ -2893,7 +2910,7 @@
         <v>23</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>24</v>
@@ -2926,7 +2943,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>44</v>
@@ -2935,7 +2952,7 @@
         <v>27</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>29</v>
@@ -3113,19 +3130,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J6" s="1">
         <v>3</v>
@@ -3140,7 +3157,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3151,19 +3168,19 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="I7" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J7" s="1">
         <v>20</v>
@@ -3178,7 +3195,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3189,19 +3206,19 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J8" s="1">
         <v>5</v>
@@ -3216,7 +3233,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3227,19 +3244,19 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
@@ -3254,7 +3271,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3265,19 +3282,19 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J10" s="1">
         <v>10</v>
@@ -3292,7 +3309,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3303,19 +3320,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J11" s="1">
         <v>10</v>
@@ -3330,7 +3347,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3341,19 +3358,19 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J12" s="1">
         <v>10</v>
@@ -3368,7 +3385,7 @@
         <v>11</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3385,19 +3402,19 @@
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -3412,7 +3429,7 @@
         <v>12</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3429,19 +3446,19 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
@@ -3456,7 +3473,7 @@
         <v>13</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3473,19 +3490,19 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J15" s="1">
         <v>15</v>
@@ -3500,7 +3517,7 @@
         <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3517,19 +3534,19 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J16" s="1">
         <v>15</v>
@@ -3544,7 +3561,7 @@
         <v>15</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3561,19 +3578,19 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J17" s="1">
         <v>15</v>
@@ -3588,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:14">

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="140">
   <si>
     <t>#</t>
   </si>
@@ -1430,7 +1430,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N41"/>
+  <dimension ref="C1:N41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1963,7 +1963,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:13">
+    <row r="17" customHeight="1" spans="3:13">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:13">
+    <row r="18" customHeight="1" spans="3:13">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:13">
+    <row r="19" customHeight="1" spans="3:13">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:13">
+    <row r="20" customHeight="1" spans="3:13">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:13">
+    <row r="21" customHeight="1" spans="3:13">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:13">
+    <row r="22" customHeight="1" spans="3:13">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:13">
+    <row r="23" customHeight="1" spans="3:13">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -2215,18 +2215,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:13">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="24" customHeight="1" spans="3:13">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>61</v>
@@ -2257,18 +2251,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:13">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="25" customHeight="1" spans="3:13">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>63</v>
@@ -2299,18 +2287,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:13">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="26" customHeight="1" spans="3:13">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>64</v>
@@ -2341,18 +2323,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:13">
-      <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="27" customHeight="1" spans="3:13">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>66</v>
@@ -2383,18 +2359,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:13">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="28" customHeight="1" spans="3:13">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>68</v>
@@ -2425,18 +2395,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:13">
-      <c r="A29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="29" customHeight="1" spans="3:13">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>69</v>
@@ -2467,18 +2431,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:13">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="30" customHeight="1" spans="3:13">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>71</v>
@@ -2509,18 +2467,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:13">
-      <c r="A31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="31" customHeight="1" spans="3:13">
       <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>73</v>
@@ -2551,18 +2503,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:13">
-      <c r="A32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="32" customHeight="1" spans="3:13">
       <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>74</v>
@@ -2593,18 +2539,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:13">
-      <c r="A33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="33" customHeight="1" spans="3:13">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>76</v>
@@ -2635,18 +2575,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:13">
-      <c r="A34" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="34" customHeight="1" spans="3:13">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>77</v>
@@ -2677,18 +2611,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:13">
-      <c r="A35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="35" customHeight="1" spans="3:13">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>78</v>
@@ -2719,18 +2647,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:13">
-      <c r="A36" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="36" customHeight="1" spans="3:13">
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>80</v>
@@ -2761,18 +2683,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:13">
-      <c r="A37" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="37" customHeight="1" spans="3:13">
       <c r="C37" s="1">
         <v>32</v>
       </c>
       <c r="D37" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>82</v>
@@ -2803,18 +2719,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:13">
-      <c r="A38" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="38" customHeight="1" spans="3:13">
       <c r="C38" s="1">
         <v>33</v>
       </c>
       <c r="D38" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>83</v>
@@ -2845,18 +2755,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:13">
-      <c r="A39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="39" customHeight="1" spans="3:13">
       <c r="C39" s="1">
         <v>34</v>
       </c>
       <c r="D39" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>85</v>
@@ -2887,18 +2791,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:13">
-      <c r="A40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="40" customHeight="1" spans="3:13">
       <c r="C40" s="1">
         <v>35</v>
       </c>
       <c r="D40" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>87</v>
@@ -2929,18 +2827,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:13">
-      <c r="A41" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="41" customHeight="1" spans="3:13">
       <c r="C41" s="1">
         <v>36</v>
       </c>
       <c r="D41" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>88</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="11480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="140">
   <si>
     <t>#</t>
   </si>
@@ -3281,12 +3281,6 @@
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C13" s="1">
         <v>1108</v>
       </c>
@@ -3325,12 +3319,6 @@
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C14" s="1">
         <v>1109</v>
       </c>
@@ -3369,12 +3357,6 @@
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C15" s="1">
         <v>1110</v>
       </c>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="137">
   <si>
     <t>#</t>
   </si>
@@ -401,22 +401,13 @@
     <t>Player/Boss/Boss8</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>幸运</t>
-  </si>
-  <si>
     <t>诅咒祭坛</t>
   </si>
   <si>
     <t>Player/Boss/Boss9</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>诅咒</t>
+    <t>增伤</t>
   </si>
   <si>
     <t>虚空裂谷</t>
@@ -425,10 +416,10 @@
     <t>Player/Boss/Boss10</t>
   </si>
   <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>生命增幅</t>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>生命倍率</t>
   </si>
   <si>
     <t>龙眠之地</t>
@@ -437,10 +428,10 @@
     <t>Player/Boss/Boss11</t>
   </si>
   <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>防御增幅</t>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
   </si>
   <si>
     <t>永恒神界</t>
@@ -449,10 +440,10 @@
     <t>Player/Boss/Boss12</t>
   </si>
   <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>攻击增幅</t>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
   </si>
 </sst>
 </file>
@@ -2877,7 +2868,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N18"/>
+  <dimension ref="C1:N18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2888,19 +2879,19 @@
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="F1" s="2"/>
       <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="F2" s="2"/>
       <c r="N2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2938,7 +2929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2976,7 +2967,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -3014,7 +3005,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="1">
         <v>1101</v>
       </c>
@@ -3052,7 +3043,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="1">
         <v>1102</v>
       </c>
@@ -3090,7 +3081,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="1">
         <v>1103</v>
       </c>
@@ -3128,7 +3119,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C9" s="1">
         <v>1104</v>
       </c>
@@ -3166,7 +3157,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C10" s="1">
         <v>1105</v>
       </c>
@@ -3204,7 +3195,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C11" s="1">
         <v>1106</v>
       </c>
@@ -3242,7 +3233,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C12" s="1">
         <v>1107</v>
       </c>
@@ -3280,7 +3271,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C13" s="1">
         <v>1108</v>
       </c>
@@ -3300,10 +3291,10 @@
         <v>93</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="J13" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K13" s="1">
         <v>10</v>
@@ -3315,10 +3306,10 @@
         <v>12</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C14" s="1">
         <v>1109</v>
       </c>
@@ -3326,10 +3317,10 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>92</v>
@@ -3338,10 +3329,10 @@
         <v>93</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="J14" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K14" s="1">
         <v>10</v>
@@ -3353,10 +3344,10 @@
         <v>13</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C15" s="1">
         <v>1110</v>
       </c>
@@ -3364,10 +3355,10 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>92</v>
@@ -3376,10 +3367,10 @@
         <v>93</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J15" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K15" s="1">
         <v>10</v>
@@ -3391,16 +3382,10 @@
         <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C16" s="1">
         <v>1111</v>
       </c>
@@ -3408,10 +3393,10 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>92</v>
@@ -3420,10 +3405,10 @@
         <v>93</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J16" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K16" s="1">
         <v>10</v>
@@ -3435,16 +3420,10 @@
         <v>15</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C17" s="1">
         <v>1112</v>
       </c>
@@ -3452,10 +3431,10 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>92</v>
@@ -3464,10 +3443,10 @@
         <v>93</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J17" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K17" s="1">
         <v>10</v>
@@ -3479,10 +3458,10 @@
         <v>16</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:14">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:14">
       <c r="F18" s="2"/>
     </row>
   </sheetData>
